--- a/invoices.xlsx
+++ b/invoices.xlsx
@@ -1202,6 +1202,9 @@
       <c r="Q18" t="str">
         <v>2026-01-02</v>
       </c>
+      <c r="R18">
+        <v>13</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
@@ -1255,6 +1258,9 @@
       <c r="Q19" t="str">
         <v>2026-01-02</v>
       </c>
+      <c r="R19" t="str">
+        <v>14</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
@@ -1308,6 +1314,9 @@
       <c r="Q20" t="str">
         <v>2026-01-02</v>
       </c>
+      <c r="R20" t="str">
+        <v>15</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
@@ -1361,6 +1370,9 @@
       <c r="Q21" t="str">
         <v>2026-01-02</v>
       </c>
+      <c r="R21" t="str">
+        <v>16</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
@@ -1414,6 +1426,9 @@
       <c r="Q22" t="str">
         <v>2026-01-02</v>
       </c>
+      <c r="R22" t="str">
+        <v>17</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
@@ -1467,6 +1482,9 @@
       <c r="Q23" t="str">
         <v>2026-01-02</v>
       </c>
+      <c r="R23" t="str">
+        <v>18</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
@@ -1520,6 +1538,9 @@
       <c r="Q24" t="str">
         <v>2026-01-02</v>
       </c>
+      <c r="R24" t="str">
+        <v>19</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
@@ -1573,6 +1594,9 @@
       <c r="Q25" t="str">
         <v>2026-01-02</v>
       </c>
+      <c r="R25" t="str">
+        <v>20</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
@@ -1626,6 +1650,9 @@
       <c r="Q26" t="str">
         <v>2026-01-02</v>
       </c>
+      <c r="R26" t="str">
+        <v>21</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
@@ -1679,6 +1706,9 @@
       <c r="Q27" t="str">
         <v>2026-01-02</v>
       </c>
+      <c r="R27" t="str">
+        <v>22</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
@@ -1732,6 +1762,9 @@
       <c r="Q28" t="str">
         <v>2026-01-02</v>
       </c>
+      <c r="R28" t="str">
+        <v>23</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
@@ -1785,6 +1818,9 @@
       <c r="Q29" t="str">
         <v>2026-01-02</v>
       </c>
+      <c r="R29" t="str">
+        <v>24</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
@@ -1838,6 +1874,9 @@
       <c r="Q30" t="str">
         <v>2026-01-02</v>
       </c>
+      <c r="R30" t="str">
+        <v>25</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
@@ -1891,6 +1930,9 @@
       <c r="Q31" t="str">
         <v>2026-01-02</v>
       </c>
+      <c r="R31" t="str">
+        <v>26</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
@@ -1944,6 +1986,9 @@
       <c r="Q32" t="str">
         <v>2026-01-02</v>
       </c>
+      <c r="R32" t="str">
+        <v>27</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
@@ -1997,6 +2042,9 @@
       <c r="Q33" t="str">
         <v>2026-01-02</v>
       </c>
+      <c r="R33" t="str">
+        <v>28</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
@@ -2050,6 +2098,9 @@
       <c r="Q34" t="str">
         <v>2026-01-02</v>
       </c>
+      <c r="R34" t="str">
+        <v>29</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
@@ -2103,6 +2154,9 @@
       <c r="Q35" t="str">
         <v>2026-01-02</v>
       </c>
+      <c r="R35" t="str">
+        <v>30</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
@@ -2156,6 +2210,9 @@
       <c r="Q36" t="str">
         <v>2026-01-02</v>
       </c>
+      <c r="R36" t="str">
+        <v>31</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
@@ -2209,6 +2266,9 @@
       <c r="Q37" t="str">
         <v>2026-01-02</v>
       </c>
+      <c r="R37" t="str">
+        <v>32</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
@@ -2262,6 +2322,9 @@
       <c r="Q38" t="str">
         <v>2026-01-02</v>
       </c>
+      <c r="R38" t="str">
+        <v>33</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
@@ -2315,6 +2378,9 @@
       <c r="Q39" t="str">
         <v>2026-01-02</v>
       </c>
+      <c r="R39" t="str">
+        <v>34</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
@@ -2368,6 +2434,9 @@
       <c r="Q40" t="str">
         <v>2026-01-02</v>
       </c>
+      <c r="R40" t="str">
+        <v>35</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
@@ -2421,6 +2490,9 @@
       <c r="Q41" t="str">
         <v>2026-01-02</v>
       </c>
+      <c r="R41" t="str">
+        <v>36</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
@@ -2474,6 +2546,9 @@
       <c r="Q42" t="str">
         <v>2026-01-02</v>
       </c>
+      <c r="R42" t="str">
+        <v>37</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
@@ -2527,6 +2602,9 @@
       <c r="Q43" t="str">
         <v>2026-01-02</v>
       </c>
+      <c r="R43" t="str">
+        <v>38</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
@@ -2580,6 +2658,9 @@
       <c r="Q44" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R44" t="str">
+        <v>39</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
@@ -2633,6 +2714,9 @@
       <c r="Q45" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R45" t="str">
+        <v>40</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
@@ -2686,6 +2770,9 @@
       <c r="Q46" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R46" t="str">
+        <v>41</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
@@ -2739,6 +2826,9 @@
       <c r="Q47" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R47" t="str">
+        <v>42</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
@@ -2792,6 +2882,9 @@
       <c r="Q48" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R48" t="str">
+        <v>43</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
@@ -2845,6 +2938,9 @@
       <c r="Q49" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R49" t="str">
+        <v>44</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
@@ -2898,6 +2994,9 @@
       <c r="Q50" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R50" t="str">
+        <v>45</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
@@ -2951,6 +3050,9 @@
       <c r="Q51" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R51" t="str">
+        <v>46</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
@@ -3004,6 +3106,9 @@
       <c r="Q52" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R52" t="str">
+        <v>47</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
@@ -3057,6 +3162,9 @@
       <c r="Q53" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R53" t="str">
+        <v>48</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
@@ -3110,6 +3218,9 @@
       <c r="Q54" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R54" t="str">
+        <v>49</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
@@ -3163,6 +3274,9 @@
       <c r="Q55" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R55" t="str">
+        <v>50</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
@@ -3216,6 +3330,9 @@
       <c r="Q56" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R56" t="str">
+        <v>51</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
@@ -3269,6 +3386,9 @@
       <c r="Q57" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R57" t="str">
+        <v>52</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
@@ -3322,6 +3442,9 @@
       <c r="Q58" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R58" t="str">
+        <v>53</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
@@ -3375,6 +3498,9 @@
       <c r="Q59" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R59" t="str">
+        <v>54</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
@@ -3428,6 +3554,9 @@
       <c r="Q60" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R60" t="str">
+        <v>55</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
@@ -3481,6 +3610,9 @@
       <c r="Q61" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R61" t="str">
+        <v>56</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
@@ -3534,6 +3666,9 @@
       <c r="Q62" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R62" t="str">
+        <v>57</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
@@ -3587,6 +3722,9 @@
       <c r="Q63" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R63" t="str">
+        <v>58</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
@@ -3640,6 +3778,9 @@
       <c r="Q64" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R64" t="str">
+        <v>59</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
@@ -3693,6 +3834,9 @@
       <c r="Q65" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R65" t="str">
+        <v>60</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
@@ -3746,6 +3890,9 @@
       <c r="Q66" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R66" t="str">
+        <v>61</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
@@ -3799,6 +3946,9 @@
       <c r="Q67" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R67" t="str">
+        <v>62</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
@@ -3852,6 +4002,9 @@
       <c r="Q68" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R68" t="str">
+        <v>63</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
@@ -3905,6 +4058,9 @@
       <c r="Q69" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R69" t="str">
+        <v>64</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
@@ -3958,6 +4114,9 @@
       <c r="Q70" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R70" t="str">
+        <v>65</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
@@ -4011,6 +4170,9 @@
       <c r="Q71" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R71" t="str">
+        <v>66</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
@@ -4064,6 +4226,9 @@
       <c r="Q72" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R72" t="str">
+        <v>67</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
@@ -4117,6 +4282,9 @@
       <c r="Q73" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R73" t="str">
+        <v>68</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
@@ -4170,6 +4338,9 @@
       <c r="Q74" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R74" t="str">
+        <v>69</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
@@ -4223,6 +4394,9 @@
       <c r="Q75" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R75" t="str">
+        <v>70</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
@@ -4276,6 +4450,9 @@
       <c r="Q76" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R76" t="str">
+        <v>71</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
@@ -4329,6 +4506,9 @@
       <c r="Q77" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R77" t="str">
+        <v>72</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
@@ -4382,6 +4562,9 @@
       <c r="Q78" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R78" t="str">
+        <v>73</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
@@ -4435,6 +4618,9 @@
       <c r="Q79" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R79" t="str">
+        <v>74</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
@@ -4488,6 +4674,9 @@
       <c r="Q80" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R80" t="str">
+        <v>75</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
@@ -4541,6 +4730,9 @@
       <c r="Q81" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R81" t="str">
+        <v>76</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
@@ -4594,6 +4786,9 @@
       <c r="Q82" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R82" t="str">
+        <v>77</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
@@ -4647,6 +4842,9 @@
       <c r="Q83" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R83" t="str">
+        <v>78</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
@@ -4700,6 +4898,9 @@
       <c r="Q84" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R84" t="str">
+        <v>79</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
@@ -4753,6 +4954,9 @@
       <c r="Q85" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R85" t="str">
+        <v>80</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
@@ -4806,6 +5010,9 @@
       <c r="Q86" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R86" t="str">
+        <v>81</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
@@ -4859,6 +5066,9 @@
       <c r="Q87" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R87" t="str">
+        <v>82</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
@@ -4912,6 +5122,9 @@
       <c r="Q88" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R88" t="str">
+        <v>83</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
@@ -4965,6 +5178,9 @@
       <c r="Q89" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R89" t="str">
+        <v>84</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
@@ -5018,6 +5234,9 @@
       <c r="Q90" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R90" t="str">
+        <v>85</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
@@ -5071,6 +5290,9 @@
       <c r="Q91" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R91" t="str">
+        <v>86</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
@@ -5124,6 +5346,9 @@
       <c r="Q92" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R92" t="str">
+        <v>87</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
@@ -5177,6 +5402,9 @@
       <c r="Q93" t="str">
         <v>2026-01-02</v>
       </c>
+      <c r="R93" t="str">
+        <v>88</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
@@ -5230,6 +5458,9 @@
       <c r="Q94" t="str">
         <v>2026-01-02</v>
       </c>
+      <c r="R94" t="str">
+        <v>89</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
@@ -5283,6 +5514,9 @@
       <c r="Q95" t="str">
         <v>2026-01-02</v>
       </c>
+      <c r="R95" t="str">
+        <v>90</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
@@ -5336,6 +5570,9 @@
       <c r="Q96" t="str">
         <v>2026-01-02</v>
       </c>
+      <c r="R96" t="str">
+        <v>91</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
@@ -5389,6 +5626,9 @@
       <c r="Q97" t="str">
         <v>2026-01-02</v>
       </c>
+      <c r="R97" t="str">
+        <v>92</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
@@ -5442,6 +5682,9 @@
       <c r="Q98" t="str">
         <v>2026-01-02</v>
       </c>
+      <c r="R98" t="str">
+        <v>93</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
@@ -5495,6 +5738,9 @@
       <c r="Q99" t="str">
         <v>2026-01-02</v>
       </c>
+      <c r="R99" t="str">
+        <v>94</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
@@ -5548,6 +5794,9 @@
       <c r="Q100" t="str">
         <v>2026-01-02</v>
       </c>
+      <c r="R100" t="str">
+        <v>95</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
@@ -5601,6 +5850,9 @@
       <c r="Q101" t="str">
         <v>2026-01-02</v>
       </c>
+      <c r="R101" t="str">
+        <v>96</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
@@ -5654,6 +5906,9 @@
       <c r="Q102" t="str">
         <v>2026-01-02</v>
       </c>
+      <c r="R102" t="str">
+        <v>97</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
@@ -5707,6 +5962,9 @@
       <c r="Q103" t="str">
         <v>2026-01-02</v>
       </c>
+      <c r="R103" t="str">
+        <v>98</v>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
@@ -5760,6 +6018,9 @@
       <c r="Q104" t="str">
         <v>2026-01-02</v>
       </c>
+      <c r="R104" t="str">
+        <v>99</v>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
@@ -5813,6 +6074,9 @@
       <c r="Q105" t="str">
         <v>2026-01-02</v>
       </c>
+      <c r="R105" t="str">
+        <v>100</v>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
@@ -5866,6 +6130,9 @@
       <c r="Q106" t="str">
         <v>2026-01-02</v>
       </c>
+      <c r="R106" t="str">
+        <v>101</v>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
@@ -5919,6 +6186,9 @@
       <c r="Q107" t="str">
         <v>2026-01-02</v>
       </c>
+      <c r="R107" t="str">
+        <v>102</v>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
@@ -5972,6 +6242,9 @@
       <c r="Q108" t="str">
         <v>2026-01-02</v>
       </c>
+      <c r="R108" t="str">
+        <v>103</v>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
@@ -6025,6 +6298,9 @@
       <c r="Q109" t="str">
         <v>2026-01-02</v>
       </c>
+      <c r="R109" t="str">
+        <v>104</v>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
@@ -6078,6 +6354,9 @@
       <c r="Q110" t="str">
         <v>2026-01-02</v>
       </c>
+      <c r="R110" t="str">
+        <v>105</v>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
@@ -6131,6 +6410,9 @@
       <c r="Q111" t="str">
         <v>2026-01-02</v>
       </c>
+      <c r="R111" t="str">
+        <v>106</v>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
@@ -6184,6 +6466,9 @@
       <c r="Q112" t="str">
         <v>2026-01-02</v>
       </c>
+      <c r="R112" t="str">
+        <v>107</v>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
@@ -6237,6 +6522,9 @@
       <c r="Q113" t="str">
         <v>2026-01-02</v>
       </c>
+      <c r="R113" t="str">
+        <v>108</v>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
@@ -6290,6 +6578,9 @@
       <c r="Q114" t="str">
         <v>2026-01-02</v>
       </c>
+      <c r="R114" t="str">
+        <v>109</v>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
@@ -6343,6 +6634,9 @@
       <c r="Q115" t="str">
         <v>2026-01-02</v>
       </c>
+      <c r="R115" t="str">
+        <v>110</v>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
@@ -6396,6 +6690,9 @@
       <c r="Q116" t="str">
         <v>2026-01-02</v>
       </c>
+      <c r="R116" t="str">
+        <v>111</v>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
@@ -6449,6 +6746,9 @@
       <c r="Q117" t="str">
         <v>2026-01-02</v>
       </c>
+      <c r="R117" t="str">
+        <v>112</v>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
@@ -6502,6 +6802,9 @@
       <c r="Q118" t="str">
         <v>2026-01-02</v>
       </c>
+      <c r="R118" t="str">
+        <v>113</v>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
@@ -6555,6 +6858,9 @@
       <c r="Q119" t="str">
         <v>2026-01-02</v>
       </c>
+      <c r="R119" t="str">
+        <v>114</v>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
@@ -6608,6 +6914,9 @@
       <c r="Q120" t="str">
         <v>2026-01-02</v>
       </c>
+      <c r="R120" t="str">
+        <v>115</v>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
@@ -6661,6 +6970,9 @@
       <c r="Q121" t="str">
         <v>2026-01-02</v>
       </c>
+      <c r="R121" t="str">
+        <v>116</v>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
@@ -6714,6 +7026,9 @@
       <c r="Q122" t="str">
         <v>2026-01-02</v>
       </c>
+      <c r="R122" t="str">
+        <v>117</v>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
@@ -6767,6 +7082,9 @@
       <c r="Q123" t="str">
         <v>2026-01-02</v>
       </c>
+      <c r="R123" t="str">
+        <v>118</v>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
@@ -6820,6 +7138,9 @@
       <c r="Q124" t="str">
         <v>2026-01-02</v>
       </c>
+      <c r="R124" t="str">
+        <v>119</v>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
@@ -6873,6 +7194,9 @@
       <c r="Q125" t="str">
         <v>2026-01-02</v>
       </c>
+      <c r="R125" t="str">
+        <v>120</v>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
@@ -6926,6 +7250,9 @@
       <c r="Q126" t="str">
         <v>2026-01-02</v>
       </c>
+      <c r="R126" t="str">
+        <v>121</v>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
@@ -6979,6 +7306,9 @@
       <c r="Q127" t="str">
         <v>2026-01-02</v>
       </c>
+      <c r="R127" t="str">
+        <v>122</v>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
@@ -7032,6 +7362,9 @@
       <c r="Q128" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R128" t="str">
+        <v>123</v>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
@@ -7085,6 +7418,9 @@
       <c r="Q129" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R129" t="str">
+        <v>124</v>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
@@ -7138,6 +7474,9 @@
       <c r="Q130" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R130" t="str">
+        <v>125</v>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
@@ -7191,6 +7530,9 @@
       <c r="Q131" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R131" t="str">
+        <v>126</v>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
@@ -7244,6 +7586,9 @@
       <c r="Q132" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R132" t="str">
+        <v>127</v>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
@@ -7297,6 +7642,9 @@
       <c r="Q133" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R133" t="str">
+        <v>128</v>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
@@ -7350,6 +7698,9 @@
       <c r="Q134" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R134" t="str">
+        <v>129</v>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
@@ -7403,6 +7754,9 @@
       <c r="Q135" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R135" t="str">
+        <v>130</v>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
@@ -7456,6 +7810,9 @@
       <c r="Q136" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R136" t="str">
+        <v>131</v>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
@@ -7509,6 +7866,9 @@
       <c r="Q137" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R137" t="str">
+        <v>132</v>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
@@ -7562,6 +7922,9 @@
       <c r="Q138" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R138" t="str">
+        <v>133</v>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
@@ -7615,6 +7978,9 @@
       <c r="Q139" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R139" t="str">
+        <v>134</v>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
@@ -7668,6 +8034,9 @@
       <c r="Q140" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R140" t="str">
+        <v>135</v>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
@@ -7721,6 +8090,9 @@
       <c r="Q141" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R141" t="str">
+        <v>136</v>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
@@ -7774,6 +8146,9 @@
       <c r="Q142" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R142" t="str">
+        <v>137</v>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
@@ -7827,6 +8202,9 @@
       <c r="Q143" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R143" t="str">
+        <v>138</v>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
@@ -7880,6 +8258,9 @@
       <c r="Q144" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R144" t="str">
+        <v>139</v>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
@@ -7933,6 +8314,9 @@
       <c r="Q145" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R145" t="str">
+        <v>140</v>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
@@ -7986,6 +8370,9 @@
       <c r="Q146" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R146" t="str">
+        <v>141</v>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
@@ -8039,6 +8426,9 @@
       <c r="Q147" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R147" t="str">
+        <v>142</v>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
@@ -8092,6 +8482,9 @@
       <c r="Q148" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R148" t="str">
+        <v>143</v>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
@@ -8145,6 +8538,9 @@
       <c r="Q149" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R149" t="str">
+        <v>144</v>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
@@ -8198,6 +8594,9 @@
       <c r="Q150" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R150" t="str">
+        <v>145</v>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
@@ -8251,6 +8650,9 @@
       <c r="Q151" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R151" t="str">
+        <v>146</v>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
@@ -8304,6 +8706,9 @@
       <c r="Q152" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R152" t="str">
+        <v>147</v>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
@@ -8357,6 +8762,9 @@
       <c r="Q153" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R153" t="str">
+        <v>148</v>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
@@ -8410,6 +8818,9 @@
       <c r="Q154" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R154" t="str">
+        <v>149</v>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
@@ -8463,6 +8874,9 @@
       <c r="Q155" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R155" t="str">
+        <v>150</v>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
@@ -8516,6 +8930,9 @@
       <c r="Q156" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R156" t="str">
+        <v>151</v>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
@@ -8569,6 +8986,9 @@
       <c r="Q157" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R157" t="str">
+        <v>152</v>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
@@ -8622,6 +9042,9 @@
       <c r="Q158" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R158" t="str">
+        <v>153</v>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
@@ -8675,6 +9098,9 @@
       <c r="Q159" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R159" t="str">
+        <v>154</v>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
@@ -8728,6 +9154,9 @@
       <c r="Q160" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R160" t="str">
+        <v>155</v>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
@@ -8781,6 +9210,9 @@
       <c r="Q161" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R161" t="str">
+        <v>156</v>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
@@ -8834,6 +9266,9 @@
       <c r="Q162" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R162" t="str">
+        <v>157</v>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
@@ -8887,6 +9322,9 @@
       <c r="Q163" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R163" t="str">
+        <v>158</v>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
@@ -8940,6 +9378,9 @@
       <c r="Q164" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R164" t="str">
+        <v>159</v>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
@@ -8993,6 +9434,9 @@
       <c r="Q165" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R165" t="str">
+        <v>160</v>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
@@ -9046,6 +9490,9 @@
       <c r="Q166" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R166" t="str">
+        <v>161</v>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
@@ -9099,6 +9546,9 @@
       <c r="Q167" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R167" t="str">
+        <v>162</v>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
@@ -9152,6 +9602,9 @@
       <c r="Q168" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R168" t="str">
+        <v>163</v>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
@@ -9205,6 +9658,9 @@
       <c r="Q169" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R169" t="str">
+        <v>164</v>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
@@ -9258,6 +9714,9 @@
       <c r="Q170" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R170" t="str">
+        <v>165</v>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
@@ -9311,6 +9770,9 @@
       <c r="Q171" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R171" t="str">
+        <v>166</v>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
@@ -9364,6 +9826,9 @@
       <c r="Q172" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R172" t="str">
+        <v>167</v>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
@@ -9417,6 +9882,9 @@
       <c r="Q173" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R173" t="str">
+        <v>168</v>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
@@ -9470,6 +9938,9 @@
       <c r="Q174" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R174" t="str">
+        <v>169</v>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
@@ -9523,6 +9994,9 @@
       <c r="Q175" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R175" t="str">
+        <v>170</v>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
@@ -9576,6 +10050,9 @@
       <c r="Q176" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R176" t="str">
+        <v>171</v>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
@@ -9629,6 +10106,9 @@
       <c r="Q177" t="str">
         <v>2026-01-02</v>
       </c>
+      <c r="R177" t="str">
+        <v>172</v>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
@@ -9682,6 +10162,9 @@
       <c r="Q178" t="str">
         <v>2026-01-02</v>
       </c>
+      <c r="R178" t="str">
+        <v>173</v>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
@@ -9735,6 +10218,9 @@
       <c r="Q179" t="str">
         <v>2026-01-02</v>
       </c>
+      <c r="R179" t="str">
+        <v>174</v>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
@@ -9788,6 +10274,9 @@
       <c r="Q180" t="str">
         <v>2026-01-02</v>
       </c>
+      <c r="R180" t="str">
+        <v>175</v>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
@@ -9841,6 +10330,9 @@
       <c r="Q181" t="str">
         <v>2026-01-02</v>
       </c>
+      <c r="R181" t="str">
+        <v>176</v>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
@@ -9894,6 +10386,9 @@
       <c r="Q182" t="str">
         <v>2026-01-02</v>
       </c>
+      <c r="R182" t="str">
+        <v>177</v>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
@@ -9947,6 +10442,9 @@
       <c r="Q183" t="str">
         <v>2026-01-02</v>
       </c>
+      <c r="R183" t="str">
+        <v>178</v>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
@@ -10000,6 +10498,9 @@
       <c r="Q184" t="str">
         <v>2026-01-02</v>
       </c>
+      <c r="R184" t="str">
+        <v>179</v>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
@@ -10053,6 +10554,9 @@
       <c r="Q185" t="str">
         <v>2026-01-02</v>
       </c>
+      <c r="R185" t="str">
+        <v>180</v>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
@@ -10106,6 +10610,9 @@
       <c r="Q186" t="str">
         <v>2026-01-02</v>
       </c>
+      <c r="R186" t="str">
+        <v>181</v>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
@@ -10159,6 +10666,9 @@
       <c r="Q187" t="str">
         <v>2026-01-02</v>
       </c>
+      <c r="R187" t="str">
+        <v>182</v>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
@@ -10212,6 +10722,9 @@
       <c r="Q188" t="str">
         <v>2026-01-02</v>
       </c>
+      <c r="R188" t="str">
+        <v>183</v>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
@@ -10265,6 +10778,9 @@
       <c r="Q189" t="str">
         <v>2026-01-02</v>
       </c>
+      <c r="R189" t="str">
+        <v>184</v>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
@@ -10318,6 +10834,9 @@
       <c r="Q190" t="str">
         <v>2026-01-02</v>
       </c>
+      <c r="R190" t="str">
+        <v>185</v>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="str">
@@ -10371,6 +10890,9 @@
       <c r="Q191" t="str">
         <v>2026-01-02</v>
       </c>
+      <c r="R191" t="str">
+        <v>186</v>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
@@ -10424,6 +10946,9 @@
       <c r="Q192" t="str">
         <v>2026-01-02</v>
       </c>
+      <c r="R192" t="str">
+        <v>187</v>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
@@ -10477,6 +11002,9 @@
       <c r="Q193" t="str">
         <v>2026-01-02</v>
       </c>
+      <c r="R193" t="str">
+        <v>188</v>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="str">
@@ -10530,6 +11058,9 @@
       <c r="Q194" t="str">
         <v>2026-01-02</v>
       </c>
+      <c r="R194" t="str">
+        <v>189</v>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="str">
@@ -10583,6 +11114,9 @@
       <c r="Q195" t="str">
         <v>2026-01-02</v>
       </c>
+      <c r="R195" t="str">
+        <v>190</v>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="str">
@@ -10636,6 +11170,9 @@
       <c r="Q196" t="str">
         <v>2026-01-02</v>
       </c>
+      <c r="R196" t="str">
+        <v>191</v>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="str">
@@ -10689,6 +11226,9 @@
       <c r="Q197" t="str">
         <v>2026-01-02</v>
       </c>
+      <c r="R197" t="str">
+        <v>192</v>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="str">
@@ -10742,6 +11282,9 @@
       <c r="Q198" t="str">
         <v>2026-01-02</v>
       </c>
+      <c r="R198" t="str">
+        <v>193</v>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="str">
@@ -10795,6 +11338,9 @@
       <c r="Q199" t="str">
         <v>2026-01-02</v>
       </c>
+      <c r="R199" t="str">
+        <v>194</v>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="str">
@@ -10848,6 +11394,9 @@
       <c r="Q200" t="str">
         <v>2026-01-02</v>
       </c>
+      <c r="R200" t="str">
+        <v>195</v>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="str">
@@ -10901,6 +11450,9 @@
       <c r="Q201" t="str">
         <v>2026-01-02</v>
       </c>
+      <c r="R201" t="str">
+        <v>196</v>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="str">
@@ -10954,6 +11506,9 @@
       <c r="Q202" t="str">
         <v>2026-01-02</v>
       </c>
+      <c r="R202" t="str">
+        <v>197</v>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="str">
@@ -11007,6 +11562,9 @@
       <c r="Q203" t="str">
         <v>2026-01-02</v>
       </c>
+      <c r="R203" t="str">
+        <v>198</v>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="str">
@@ -11060,6 +11618,9 @@
       <c r="Q204" t="str">
         <v>2026-01-02</v>
       </c>
+      <c r="R204" t="str">
+        <v>199</v>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="str">
@@ -11113,6 +11674,9 @@
       <c r="Q205" t="str">
         <v>2026-01-02</v>
       </c>
+      <c r="R205" t="str">
+        <v>200</v>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="str">
@@ -11166,6 +11730,9 @@
       <c r="Q206" t="str">
         <v>2026-01-02</v>
       </c>
+      <c r="R206" t="str">
+        <v>201</v>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="str">
@@ -11219,6 +11786,9 @@
       <c r="Q207" t="str">
         <v>2026-01-02</v>
       </c>
+      <c r="R207" t="str">
+        <v>202</v>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="str">
@@ -11272,6 +11842,9 @@
       <c r="Q208" t="str">
         <v>2026-01-02</v>
       </c>
+      <c r="R208" t="str">
+        <v>203</v>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="str">
@@ -11325,6 +11898,9 @@
       <c r="Q209" t="str">
         <v>2026-01-02</v>
       </c>
+      <c r="R209" t="str">
+        <v>204</v>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="str">
@@ -11378,6 +11954,9 @@
       <c r="Q210" t="str">
         <v>2026-01-02</v>
       </c>
+      <c r="R210" t="str">
+        <v>205</v>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="str">
@@ -11431,6 +12010,9 @@
       <c r="Q211" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R211" t="str">
+        <v>206</v>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="str">
@@ -11484,6 +12066,9 @@
       <c r="Q212" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R212" t="str">
+        <v>207</v>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="str">
@@ -11537,6 +12122,9 @@
       <c r="Q213" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R213" t="str">
+        <v>208</v>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="str">
@@ -11590,6 +12178,9 @@
       <c r="Q214" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R214" t="str">
+        <v>209</v>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="str">
@@ -11643,6 +12234,9 @@
       <c r="Q215" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R215" t="str">
+        <v>210</v>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="str">
@@ -11696,6 +12290,9 @@
       <c r="Q216" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R216" t="str">
+        <v>211</v>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="str">
@@ -11749,6 +12346,9 @@
       <c r="Q217" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R217" t="str">
+        <v>212</v>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="str">
@@ -11802,6 +12402,9 @@
       <c r="Q218" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R218" t="str">
+        <v>213</v>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="str">
@@ -11855,6 +12458,9 @@
       <c r="Q219" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R219" t="str">
+        <v>214</v>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="str">
@@ -11908,6 +12514,9 @@
       <c r="Q220" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R220" t="str">
+        <v>215</v>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="str">
@@ -11961,6 +12570,9 @@
       <c r="Q221" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R221" t="str">
+        <v>216</v>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="str">
@@ -12014,6 +12626,9 @@
       <c r="Q222" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R222" t="str">
+        <v>217</v>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="str">
@@ -12067,6 +12682,9 @@
       <c r="Q223" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R223" t="str">
+        <v>218</v>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="str">
@@ -12120,6 +12738,9 @@
       <c r="Q224" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R224" t="str">
+        <v>219</v>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="str">
@@ -12173,6 +12794,9 @@
       <c r="Q225" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R225" t="str">
+        <v>220</v>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="str">
@@ -12226,6 +12850,9 @@
       <c r="Q226" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R226" t="str">
+        <v>221</v>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="str">
@@ -12279,6 +12906,9 @@
       <c r="Q227" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R227" t="str">
+        <v>222</v>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="str">
@@ -12332,6 +12962,9 @@
       <c r="Q228" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R228" t="str">
+        <v>223</v>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="str">
@@ -12385,6 +13018,9 @@
       <c r="Q229" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R229" t="str">
+        <v>224</v>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="str">
@@ -12438,6 +13074,9 @@
       <c r="Q230" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R230" t="str">
+        <v>225</v>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="str">
@@ -12491,6 +13130,9 @@
       <c r="Q231" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R231" t="str">
+        <v>226</v>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="str">
@@ -12544,6 +13186,9 @@
       <c r="Q232" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R232" t="str">
+        <v>227</v>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="str">
@@ -12597,6 +13242,9 @@
       <c r="Q233" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R233" t="str">
+        <v>228</v>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="str">
@@ -12650,6 +13298,9 @@
       <c r="Q234" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R234" t="str">
+        <v>229</v>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="str">
@@ -12703,6 +13354,9 @@
       <c r="Q235" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R235" t="str">
+        <v>230</v>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="str">
@@ -12756,6 +13410,9 @@
       <c r="Q236" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R236" t="str">
+        <v>231</v>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="str">
@@ -12809,6 +13466,9 @@
       <c r="Q237" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R237" t="str">
+        <v>232</v>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="str">
@@ -12862,6 +13522,9 @@
       <c r="Q238" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R238" t="str">
+        <v>233</v>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="str">
@@ -12915,6 +13578,9 @@
       <c r="Q239" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R239" t="str">
+        <v>234</v>
+      </c>
     </row>
     <row r="240">
       <c r="A240" t="str">
@@ -12968,6 +13634,9 @@
       <c r="Q240" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R240" t="str">
+        <v>235</v>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="str">
@@ -13021,6 +13690,9 @@
       <c r="Q241" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R241" t="str">
+        <v>236</v>
+      </c>
     </row>
     <row r="242">
       <c r="A242" t="str">
@@ -13074,6 +13746,9 @@
       <c r="Q242" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R242" t="str">
+        <v>237</v>
+      </c>
     </row>
     <row r="243">
       <c r="A243" t="str">
@@ -13127,6 +13802,9 @@
       <c r="Q243" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R243" t="str">
+        <v>238</v>
+      </c>
     </row>
     <row r="244">
       <c r="A244" t="str">
@@ -13180,6 +13858,9 @@
       <c r="Q244" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R244" t="str">
+        <v>239</v>
+      </c>
     </row>
     <row r="245">
       <c r="A245" t="str">
@@ -13233,6 +13914,9 @@
       <c r="Q245" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R245" t="str">
+        <v>240</v>
+      </c>
     </row>
     <row r="246">
       <c r="A246" t="str">
@@ -13286,6 +13970,9 @@
       <c r="Q246" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R246" t="str">
+        <v>241</v>
+      </c>
     </row>
     <row r="247">
       <c r="A247" t="str">
@@ -13339,6 +14026,9 @@
       <c r="Q247" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R247" t="str">
+        <v>242</v>
+      </c>
     </row>
     <row r="248">
       <c r="A248" t="str">
@@ -13392,6 +14082,9 @@
       <c r="Q248" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R248" t="str">
+        <v>243</v>
+      </c>
     </row>
     <row r="249">
       <c r="A249" t="str">
@@ -13445,6 +14138,9 @@
       <c r="Q249" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R249" t="str">
+        <v>244</v>
+      </c>
     </row>
     <row r="250">
       <c r="A250" t="str">
@@ -13498,6 +14194,9 @@
       <c r="Q250" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R250" t="str">
+        <v>245</v>
+      </c>
     </row>
     <row r="251">
       <c r="A251" t="str">
@@ -13551,6 +14250,9 @@
       <c r="Q251" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R251" t="str">
+        <v>246</v>
+      </c>
     </row>
     <row r="252">
       <c r="A252" t="str">
@@ -13604,6 +14306,9 @@
       <c r="Q252" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R252" t="str">
+        <v>247</v>
+      </c>
     </row>
     <row r="253">
       <c r="A253" t="str">
@@ -13657,6 +14362,9 @@
       <c r="Q253" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R253" t="str">
+        <v>248</v>
+      </c>
     </row>
     <row r="254">
       <c r="A254" t="str">
@@ -13710,6 +14418,9 @@
       <c r="Q254" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R254" t="str">
+        <v>249</v>
+      </c>
     </row>
     <row r="255">
       <c r="A255" t="str">
@@ -13763,6 +14474,9 @@
       <c r="Q255" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R255" t="str">
+        <v>250</v>
+      </c>
     </row>
     <row r="256">
       <c r="A256" t="str">
@@ -13816,6 +14530,9 @@
       <c r="Q256" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R256" t="str">
+        <v>251</v>
+      </c>
     </row>
     <row r="257">
       <c r="A257" t="str">
@@ -13869,6 +14586,9 @@
       <c r="Q257" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R257" t="str">
+        <v>252</v>
+      </c>
     </row>
     <row r="258">
       <c r="A258" t="str">
@@ -13922,6 +14642,9 @@
       <c r="Q258" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R258" t="str">
+        <v>253</v>
+      </c>
     </row>
     <row r="259">
       <c r="A259" t="str">
@@ -13975,6 +14698,9 @@
       <c r="Q259" t="str">
         <v>2026-01-02</v>
       </c>
+      <c r="R259" t="str">
+        <v>254</v>
+      </c>
     </row>
     <row r="260">
       <c r="A260" t="str">
@@ -14028,6 +14754,9 @@
       <c r="Q260" t="str">
         <v>2026-01-02</v>
       </c>
+      <c r="R260" t="str">
+        <v>255</v>
+      </c>
     </row>
     <row r="261">
       <c r="A261" t="str">
@@ -14081,6 +14810,9 @@
       <c r="Q261" t="str">
         <v>2026-01-02</v>
       </c>
+      <c r="R261" t="str">
+        <v>256</v>
+      </c>
     </row>
     <row r="262">
       <c r="A262" t="str">
@@ -14134,6 +14866,9 @@
       <c r="Q262" t="str">
         <v>2026-01-02</v>
       </c>
+      <c r="R262" t="str">
+        <v>257</v>
+      </c>
     </row>
     <row r="263">
       <c r="A263" t="str">
@@ -14187,6 +14922,9 @@
       <c r="Q263" t="str">
         <v>2026-01-02</v>
       </c>
+      <c r="R263" t="str">
+        <v>258</v>
+      </c>
     </row>
     <row r="264">
       <c r="A264" t="str">
@@ -14240,6 +14978,9 @@
       <c r="Q264" t="str">
         <v>2026-01-02</v>
       </c>
+      <c r="R264" t="str">
+        <v>259</v>
+      </c>
     </row>
     <row r="265">
       <c r="A265" t="str">
@@ -14293,6 +15034,9 @@
       <c r="Q265" t="str">
         <v>2026-01-02</v>
       </c>
+      <c r="R265" t="str">
+        <v>260</v>
+      </c>
     </row>
     <row r="266">
       <c r="A266" t="str">
@@ -14346,6 +15090,9 @@
       <c r="Q266" t="str">
         <v>2026-01-02</v>
       </c>
+      <c r="R266" t="str">
+        <v>261</v>
+      </c>
     </row>
     <row r="267">
       <c r="A267" t="str">
@@ -14399,6 +15146,9 @@
       <c r="Q267" t="str">
         <v>2026-01-02</v>
       </c>
+      <c r="R267" t="str">
+        <v>262</v>
+      </c>
     </row>
     <row r="268">
       <c r="A268" t="str">
@@ -14452,6 +15202,9 @@
       <c r="Q268" t="str">
         <v>2026-01-02</v>
       </c>
+      <c r="R268" t="str">
+        <v>263</v>
+      </c>
     </row>
     <row r="269">
       <c r="A269" t="str">
@@ -14505,6 +15258,9 @@
       <c r="Q269" t="str">
         <v>2026-01-02</v>
       </c>
+      <c r="R269" t="str">
+        <v>264</v>
+      </c>
     </row>
     <row r="270">
       <c r="A270" t="str">
@@ -14558,6 +15314,9 @@
       <c r="Q270" t="str">
         <v>2026-01-02</v>
       </c>
+      <c r="R270" t="str">
+        <v>265</v>
+      </c>
     </row>
     <row r="271">
       <c r="A271" t="str">
@@ -14611,6 +15370,9 @@
       <c r="Q271" t="str">
         <v>2026-01-02</v>
       </c>
+      <c r="R271" t="str">
+        <v>266</v>
+      </c>
     </row>
     <row r="272">
       <c r="A272" t="str">
@@ -14664,6 +15426,9 @@
       <c r="Q272" t="str">
         <v>2026-01-02</v>
       </c>
+      <c r="R272" t="str">
+        <v>267</v>
+      </c>
     </row>
     <row r="273">
       <c r="A273" t="str">
@@ -14717,6 +15482,9 @@
       <c r="Q273" t="str">
         <v>2026-01-02</v>
       </c>
+      <c r="R273" t="str">
+        <v>268</v>
+      </c>
     </row>
     <row r="274">
       <c r="A274" t="str">
@@ -14770,6 +15538,9 @@
       <c r="Q274" t="str">
         <v>2026-01-02</v>
       </c>
+      <c r="R274" t="str">
+        <v>269</v>
+      </c>
     </row>
     <row r="275">
       <c r="A275" t="str">
@@ -14823,6 +15594,9 @@
       <c r="Q275" t="str">
         <v>2026-01-02</v>
       </c>
+      <c r="R275" t="str">
+        <v>270</v>
+      </c>
     </row>
     <row r="276">
       <c r="A276" t="str">
@@ -14876,6 +15650,9 @@
       <c r="Q276" t="str">
         <v>2026-01-02</v>
       </c>
+      <c r="R276" t="str">
+        <v>271</v>
+      </c>
     </row>
     <row r="277">
       <c r="A277" t="str">
@@ -14929,6 +15706,9 @@
       <c r="Q277" t="str">
         <v>2026-01-02</v>
       </c>
+      <c r="R277" t="str">
+        <v>272</v>
+      </c>
     </row>
     <row r="278">
       <c r="A278" t="str">
@@ -14982,6 +15762,9 @@
       <c r="Q278" t="str">
         <v>2026-01-02</v>
       </c>
+      <c r="R278" t="str">
+        <v>273</v>
+      </c>
     </row>
     <row r="279">
       <c r="A279" t="str">
@@ -15035,6 +15818,9 @@
       <c r="Q279" t="str">
         <v>2026-01-02</v>
       </c>
+      <c r="R279" t="str">
+        <v>274</v>
+      </c>
     </row>
     <row r="280">
       <c r="A280" t="str">
@@ -15088,6 +15874,9 @@
       <c r="Q280" t="str">
         <v>2026-01-02</v>
       </c>
+      <c r="R280" t="str">
+        <v>275</v>
+      </c>
     </row>
     <row r="281">
       <c r="A281" t="str">
@@ -15141,6 +15930,9 @@
       <c r="Q281" t="str">
         <v>2026-01-02</v>
       </c>
+      <c r="R281" t="str">
+        <v>276</v>
+      </c>
     </row>
     <row r="282">
       <c r="A282" t="str">
@@ -15194,6 +15986,9 @@
       <c r="Q282" t="str">
         <v>2026-01-02</v>
       </c>
+      <c r="R282" t="str">
+        <v>277</v>
+      </c>
     </row>
     <row r="283">
       <c r="A283" t="str">
@@ -15247,6 +16042,9 @@
       <c r="Q283" t="str">
         <v>2026-01-02</v>
       </c>
+      <c r="R283" t="str">
+        <v>278</v>
+      </c>
     </row>
     <row r="284">
       <c r="A284" t="str">
@@ -15300,6 +16098,9 @@
       <c r="Q284" t="str">
         <v>2026-01-02</v>
       </c>
+      <c r="R284" t="str">
+        <v>279</v>
+      </c>
     </row>
     <row r="285">
       <c r="A285" t="str">
@@ -15353,6 +16154,9 @@
       <c r="Q285" t="str">
         <v>2026-01-02</v>
       </c>
+      <c r="R285" t="str">
+        <v>280</v>
+      </c>
     </row>
     <row r="286">
       <c r="A286" t="str">
@@ -15406,6 +16210,9 @@
       <c r="Q286" t="str">
         <v>2026-01-02</v>
       </c>
+      <c r="R286" t="str">
+        <v>281</v>
+      </c>
     </row>
     <row r="287">
       <c r="A287" t="str">
@@ -15459,6 +16266,9 @@
       <c r="Q287" t="str">
         <v>2026-01-02</v>
       </c>
+      <c r="R287" t="str">
+        <v>282</v>
+      </c>
     </row>
     <row r="288">
       <c r="A288" t="str">
@@ -15512,6 +16322,9 @@
       <c r="Q288" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R288" t="str">
+        <v>283</v>
+      </c>
     </row>
     <row r="289">
       <c r="A289" t="str">
@@ -15565,6 +16378,9 @@
       <c r="Q289" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R289" t="str">
+        <v>284</v>
+      </c>
     </row>
     <row r="290">
       <c r="A290" t="str">
@@ -15618,6 +16434,9 @@
       <c r="Q290" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R290" t="str">
+        <v>285</v>
+      </c>
     </row>
     <row r="291">
       <c r="A291" t="str">
@@ -15671,6 +16490,9 @@
       <c r="Q291" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R291" t="str">
+        <v>286</v>
+      </c>
     </row>
     <row r="292">
       <c r="A292" t="str">
@@ -15724,6 +16546,9 @@
       <c r="Q292" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R292" t="str">
+        <v>287</v>
+      </c>
     </row>
     <row r="293">
       <c r="A293" t="str">
@@ -15777,6 +16602,9 @@
       <c r="Q293" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R293" t="str">
+        <v>288</v>
+      </c>
     </row>
     <row r="294">
       <c r="A294" t="str">
@@ -15830,6 +16658,9 @@
       <c r="Q294" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R294" t="str">
+        <v>289</v>
+      </c>
     </row>
     <row r="295">
       <c r="A295" t="str">
@@ -15883,6 +16714,9 @@
       <c r="Q295" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R295" t="str">
+        <v>290</v>
+      </c>
     </row>
     <row r="296">
       <c r="A296" t="str">
@@ -15936,6 +16770,9 @@
       <c r="Q296" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R296" t="str">
+        <v>291</v>
+      </c>
     </row>
     <row r="297">
       <c r="A297" t="str">
@@ -15989,6 +16826,9 @@
       <c r="Q297" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R297" t="str">
+        <v>292</v>
+      </c>
     </row>
     <row r="298">
       <c r="A298" t="str">
@@ -16042,6 +16882,9 @@
       <c r="Q298" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R298" t="str">
+        <v>293</v>
+      </c>
     </row>
     <row r="299">
       <c r="A299" t="str">
@@ -16095,6 +16938,9 @@
       <c r="Q299" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R299" t="str">
+        <v>294</v>
+      </c>
     </row>
     <row r="300">
       <c r="A300" t="str">
@@ -16148,6 +16994,9 @@
       <c r="Q300" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R300" t="str">
+        <v>295</v>
+      </c>
     </row>
     <row r="301">
       <c r="A301" t="str">
@@ -16201,6 +17050,9 @@
       <c r="Q301" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R301" t="str">
+        <v>296</v>
+      </c>
     </row>
     <row r="302">
       <c r="A302" t="str">
@@ -16254,6 +17106,9 @@
       <c r="Q302" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R302" t="str">
+        <v>297</v>
+      </c>
     </row>
     <row r="303">
       <c r="A303" t="str">
@@ -16307,6 +17162,9 @@
       <c r="Q303" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R303" t="str">
+        <v>298</v>
+      </c>
     </row>
     <row r="304">
       <c r="A304" t="str">
@@ -16360,6 +17218,9 @@
       <c r="Q304" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R304" t="str">
+        <v>299</v>
+      </c>
     </row>
     <row r="305">
       <c r="A305" t="str">
@@ -16413,6 +17274,9 @@
       <c r="Q305" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R305" t="str">
+        <v>300</v>
+      </c>
     </row>
     <row r="306">
       <c r="A306" t="str">
@@ -16466,6 +17330,9 @@
       <c r="Q306" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R306" t="str">
+        <v>301</v>
+      </c>
     </row>
     <row r="307">
       <c r="A307" t="str">
@@ -16519,6 +17386,9 @@
       <c r="Q307" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R307" t="str">
+        <v>302</v>
+      </c>
     </row>
     <row r="308">
       <c r="A308" t="str">
@@ -16572,6 +17442,9 @@
       <c r="Q308" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R308" t="str">
+        <v>303</v>
+      </c>
     </row>
     <row r="309">
       <c r="A309" t="str">
@@ -16625,6 +17498,9 @@
       <c r="Q309" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R309" t="str">
+        <v>304</v>
+      </c>
     </row>
     <row r="310">
       <c r="A310" t="str">
@@ -16678,6 +17554,9 @@
       <c r="Q310" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R310" t="str">
+        <v>305</v>
+      </c>
     </row>
     <row r="311">
       <c r="A311" t="str">
@@ -16731,6 +17610,9 @@
       <c r="Q311" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R311" t="str">
+        <v>306</v>
+      </c>
     </row>
     <row r="312">
       <c r="A312" t="str">
@@ -16784,6 +17666,9 @@
       <c r="Q312" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R312" t="str">
+        <v>307</v>
+      </c>
     </row>
     <row r="313">
       <c r="A313" t="str">
@@ -16837,6 +17722,9 @@
       <c r="Q313" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R313" t="str">
+        <v>308</v>
+      </c>
     </row>
     <row r="314">
       <c r="A314" t="str">
@@ -16890,6 +17778,9 @@
       <c r="Q314" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R314" t="str">
+        <v>309</v>
+      </c>
     </row>
     <row r="315">
       <c r="A315" t="str">
@@ -16943,6 +17834,9 @@
       <c r="Q315" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R315" t="str">
+        <v>310</v>
+      </c>
     </row>
     <row r="316">
       <c r="A316" t="str">
@@ -16996,6 +17890,9 @@
       <c r="Q316" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R316" t="str">
+        <v>311</v>
+      </c>
     </row>
     <row r="317">
       <c r="A317" t="str">
@@ -17049,6 +17946,9 @@
       <c r="Q317" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R317" t="str">
+        <v>312</v>
+      </c>
     </row>
     <row r="318">
       <c r="A318" t="str">
@@ -17102,6 +18002,9 @@
       <c r="Q318" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R318" t="str">
+        <v>313</v>
+      </c>
     </row>
     <row r="319">
       <c r="A319" t="str">
@@ -17155,6 +18058,9 @@
       <c r="Q319" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R319" t="str">
+        <v>314</v>
+      </c>
     </row>
     <row r="320">
       <c r="A320" t="str">
@@ -17208,6 +18114,9 @@
       <c r="Q320" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R320" t="str">
+        <v>315</v>
+      </c>
     </row>
     <row r="321">
       <c r="A321" t="str">
@@ -17261,6 +18170,9 @@
       <c r="Q321" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R321" t="str">
+        <v>316</v>
+      </c>
     </row>
     <row r="322">
       <c r="A322" t="str">
@@ -17314,6 +18226,9 @@
       <c r="Q322" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R322" t="str">
+        <v>317</v>
+      </c>
     </row>
     <row r="323">
       <c r="A323" t="str">
@@ -17367,6 +18282,9 @@
       <c r="Q323" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R323" t="str">
+        <v>318</v>
+      </c>
     </row>
     <row r="324">
       <c r="A324" t="str">
@@ -17420,6 +18338,9 @@
       <c r="Q324" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R324" t="str">
+        <v>319</v>
+      </c>
     </row>
     <row r="325">
       <c r="A325" t="str">
@@ -17473,6 +18394,9 @@
       <c r="Q325" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R325" t="str">
+        <v>320</v>
+      </c>
     </row>
     <row r="326">
       <c r="A326" t="str">
@@ -17526,6 +18450,9 @@
       <c r="Q326" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R326" t="str">
+        <v>321</v>
+      </c>
     </row>
     <row r="327">
       <c r="A327" t="str">
@@ -17579,6 +18506,9 @@
       <c r="Q327" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R327" t="str">
+        <v>322</v>
+      </c>
     </row>
     <row r="328">
       <c r="A328" t="str">
@@ -17632,6 +18562,9 @@
       <c r="Q328" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R328" t="str">
+        <v>323</v>
+      </c>
     </row>
     <row r="329">
       <c r="A329" t="str">
@@ -17685,6 +18618,9 @@
       <c r="Q329" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R329" t="str">
+        <v>324</v>
+      </c>
     </row>
     <row r="330">
       <c r="A330" t="str">
@@ -17738,6 +18674,9 @@
       <c r="Q330" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R330" t="str">
+        <v>325</v>
+      </c>
     </row>
     <row r="331">
       <c r="A331" t="str">
@@ -17791,6 +18730,9 @@
       <c r="Q331" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R331" t="str">
+        <v>326</v>
+      </c>
     </row>
     <row r="332">
       <c r="A332" t="str">
@@ -17844,6 +18786,9 @@
       <c r="Q332" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R332" t="str">
+        <v>327</v>
+      </c>
     </row>
     <row r="333">
       <c r="A333" t="str">
@@ -17897,6 +18842,9 @@
       <c r="Q333" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R333" t="str">
+        <v>328</v>
+      </c>
     </row>
     <row r="334">
       <c r="A334" t="str">
@@ -17950,6 +18898,9 @@
       <c r="Q334" t="str">
         <v>2026-01-02</v>
       </c>
+      <c r="R334" t="str">
+        <v>329</v>
+      </c>
     </row>
     <row r="335">
       <c r="A335" t="str">
@@ -18003,6 +18954,9 @@
       <c r="Q335" t="str">
         <v>2026-01-02</v>
       </c>
+      <c r="R335" t="str">
+        <v>330</v>
+      </c>
     </row>
     <row r="336">
       <c r="A336" t="str">
@@ -18056,6 +19010,9 @@
       <c r="Q336" t="str">
         <v>2026-01-02</v>
       </c>
+      <c r="R336" t="str">
+        <v>331</v>
+      </c>
     </row>
     <row r="337">
       <c r="A337" t="str">
@@ -18109,6 +19066,9 @@
       <c r="Q337" t="str">
         <v>2026-01-02</v>
       </c>
+      <c r="R337" t="str">
+        <v>332</v>
+      </c>
     </row>
     <row r="338">
       <c r="A338" t="str">
@@ -18162,6 +19122,9 @@
       <c r="Q338" t="str">
         <v>2026-01-02</v>
       </c>
+      <c r="R338" t="str">
+        <v>333</v>
+      </c>
     </row>
     <row r="339">
       <c r="A339" t="str">
@@ -18215,6 +19178,9 @@
       <c r="Q339" t="str">
         <v>2026-01-02</v>
       </c>
+      <c r="R339" t="str">
+        <v>334</v>
+      </c>
     </row>
     <row r="340">
       <c r="A340" t="str">
@@ -18268,6 +19234,9 @@
       <c r="Q340" t="str">
         <v>2026-01-02</v>
       </c>
+      <c r="R340" t="str">
+        <v>335</v>
+      </c>
     </row>
     <row r="341">
       <c r="A341" t="str">
@@ -18321,6 +19290,9 @@
       <c r="Q341" t="str">
         <v>2026-01-02</v>
       </c>
+      <c r="R341" t="str">
+        <v>336</v>
+      </c>
     </row>
     <row r="342">
       <c r="A342" t="str">
@@ -18374,6 +19346,9 @@
       <c r="Q342" t="str">
         <v>2026-01-02</v>
       </c>
+      <c r="R342" t="str">
+        <v>337</v>
+      </c>
     </row>
     <row r="343">
       <c r="A343" t="str">
@@ -18427,6 +19402,9 @@
       <c r="Q343" t="str">
         <v>2026-01-02</v>
       </c>
+      <c r="R343" t="str">
+        <v>338</v>
+      </c>
     </row>
     <row r="344">
       <c r="A344" t="str">
@@ -18480,6 +19458,9 @@
       <c r="Q344" t="str">
         <v>2026-01-02</v>
       </c>
+      <c r="R344" t="str">
+        <v>339</v>
+      </c>
     </row>
     <row r="345">
       <c r="A345" t="str">
@@ -18533,6 +19514,9 @@
       <c r="Q345" t="str">
         <v>2026-01-02</v>
       </c>
+      <c r="R345" t="str">
+        <v>340</v>
+      </c>
     </row>
     <row r="346">
       <c r="A346" t="str">
@@ -18586,6 +19570,9 @@
       <c r="Q346" t="str">
         <v>2026-01-02</v>
       </c>
+      <c r="R346" t="str">
+        <v>341</v>
+      </c>
     </row>
     <row r="347">
       <c r="A347" t="str">
@@ -18639,6 +19626,9 @@
       <c r="Q347" t="str">
         <v>2026-01-02</v>
       </c>
+      <c r="R347" t="str">
+        <v>342</v>
+      </c>
     </row>
     <row r="348">
       <c r="A348" t="str">
@@ -18692,6 +19682,9 @@
       <c r="Q348" t="str">
         <v>2026-01-02</v>
       </c>
+      <c r="R348" t="str">
+        <v>343</v>
+      </c>
     </row>
     <row r="349">
       <c r="A349" t="str">
@@ -18745,6 +19738,9 @@
       <c r="Q349" t="str">
         <v>2026-01-02</v>
       </c>
+      <c r="R349" t="str">
+        <v>344</v>
+      </c>
     </row>
     <row r="350">
       <c r="A350" t="str">
@@ -18798,6 +19794,9 @@
       <c r="Q350" t="str">
         <v>2026-01-02</v>
       </c>
+      <c r="R350" t="str">
+        <v>345</v>
+      </c>
     </row>
     <row r="351">
       <c r="A351" t="str">
@@ -18851,6 +19850,9 @@
       <c r="Q351" t="str">
         <v>2026-01-02</v>
       </c>
+      <c r="R351" t="str">
+        <v>346</v>
+      </c>
     </row>
     <row r="352">
       <c r="A352" t="str">
@@ -18904,6 +19906,9 @@
       <c r="Q352" t="str">
         <v>2026-01-02</v>
       </c>
+      <c r="R352" t="str">
+        <v>347</v>
+      </c>
     </row>
     <row r="353">
       <c r="A353" t="str">
@@ -18957,6 +19962,9 @@
       <c r="Q353" t="str">
         <v>2026-01-02</v>
       </c>
+      <c r="R353" t="str">
+        <v>348</v>
+      </c>
     </row>
     <row r="354">
       <c r="A354" t="str">
@@ -19010,6 +20018,9 @@
       <c r="Q354" t="str">
         <v>2026-01-02</v>
       </c>
+      <c r="R354" t="str">
+        <v>349</v>
+      </c>
     </row>
     <row r="355">
       <c r="A355" t="str">
@@ -19063,6 +20074,9 @@
       <c r="Q355" t="str">
         <v>2026-01-02</v>
       </c>
+      <c r="R355" t="str">
+        <v>350</v>
+      </c>
     </row>
     <row r="356">
       <c r="A356" t="str">
@@ -19116,6 +20130,9 @@
       <c r="Q356" t="str">
         <v>2026-01-02</v>
       </c>
+      <c r="R356" t="str">
+        <v>351</v>
+      </c>
     </row>
     <row r="357">
       <c r="A357" t="str">
@@ -19169,6 +20186,9 @@
       <c r="Q357" t="str">
         <v>2026-01-02</v>
       </c>
+      <c r="R357" t="str">
+        <v>352</v>
+      </c>
     </row>
     <row r="358">
       <c r="A358" t="str">
@@ -19222,6 +20242,9 @@
       <c r="Q358" t="str">
         <v>2026-01-02</v>
       </c>
+      <c r="R358" t="str">
+        <v>353</v>
+      </c>
     </row>
     <row r="359">
       <c r="A359" t="str">
@@ -19275,6 +20298,9 @@
       <c r="Q359" t="str">
         <v>2026-01-02</v>
       </c>
+      <c r="R359" t="str">
+        <v>354</v>
+      </c>
     </row>
     <row r="360">
       <c r="A360" t="str">
@@ -19328,6 +20354,9 @@
       <c r="Q360" t="str">
         <v>2026-01-02</v>
       </c>
+      <c r="R360" t="str">
+        <v>355</v>
+      </c>
     </row>
     <row r="361">
       <c r="A361" t="str">
@@ -19381,6 +20410,9 @@
       <c r="Q361" t="str">
         <v>2026-01-02</v>
       </c>
+      <c r="R361" t="str">
+        <v>356</v>
+      </c>
     </row>
     <row r="362">
       <c r="A362" t="str">
@@ -19434,6 +20466,9 @@
       <c r="Q362" t="str">
         <v>2026-01-02</v>
       </c>
+      <c r="R362" t="str">
+        <v>357</v>
+      </c>
     </row>
     <row r="363">
       <c r="A363" t="str">
@@ -19487,6 +20522,9 @@
       <c r="Q363" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R363" t="str">
+        <v>358</v>
+      </c>
     </row>
     <row r="364">
       <c r="A364" t="str">
@@ -19540,6 +20578,9 @@
       <c r="Q364" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R364" t="str">
+        <v>359</v>
+      </c>
     </row>
     <row r="365">
       <c r="A365" t="str">
@@ -19593,6 +20634,9 @@
       <c r="Q365" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R365" t="str">
+        <v>360</v>
+      </c>
     </row>
     <row r="366">
       <c r="A366" t="str">
@@ -19646,6 +20690,9 @@
       <c r="Q366" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R366" t="str">
+        <v>361</v>
+      </c>
     </row>
     <row r="367">
       <c r="A367" t="str">
@@ -19699,6 +20746,9 @@
       <c r="Q367" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R367" t="str">
+        <v>362</v>
+      </c>
     </row>
     <row r="368">
       <c r="A368" t="str">
@@ -19752,6 +20802,9 @@
       <c r="Q368" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R368" t="str">
+        <v>363</v>
+      </c>
     </row>
     <row r="369">
       <c r="A369" t="str">
@@ -19805,6 +20858,9 @@
       <c r="Q369" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R369" t="str">
+        <v>364</v>
+      </c>
     </row>
     <row r="370">
       <c r="A370" t="str">
@@ -19858,6 +20914,9 @@
       <c r="Q370" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R370" t="str">
+        <v>365</v>
+      </c>
     </row>
     <row r="371">
       <c r="A371" t="str">
@@ -19911,6 +20970,9 @@
       <c r="Q371" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R371" t="str">
+        <v>366</v>
+      </c>
     </row>
     <row r="372">
       <c r="A372" t="str">
@@ -19964,6 +21026,9 @@
       <c r="Q372" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R372" t="str">
+        <v>367</v>
+      </c>
     </row>
     <row r="373">
       <c r="A373" t="str">
@@ -20017,6 +21082,9 @@
       <c r="Q373" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R373" t="str">
+        <v>368</v>
+      </c>
     </row>
     <row r="374">
       <c r="A374" t="str">
@@ -20070,6 +21138,9 @@
       <c r="Q374" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R374" t="str">
+        <v>369</v>
+      </c>
     </row>
     <row r="375">
       <c r="A375" t="str">
@@ -20123,6 +21194,9 @@
       <c r="Q375" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R375" t="str">
+        <v>370</v>
+      </c>
     </row>
     <row r="376">
       <c r="A376" t="str">
@@ -20176,6 +21250,9 @@
       <c r="Q376" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R376" t="str">
+        <v>371</v>
+      </c>
     </row>
     <row r="377">
       <c r="A377" t="str">
@@ -20229,6 +21306,9 @@
       <c r="Q377" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R377" t="str">
+        <v>372</v>
+      </c>
     </row>
     <row r="378">
       <c r="A378" t="str">
@@ -20282,6 +21362,9 @@
       <c r="Q378" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R378" t="str">
+        <v>373</v>
+      </c>
     </row>
     <row r="379">
       <c r="A379" t="str">
@@ -20335,6 +21418,9 @@
       <c r="Q379" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R379" t="str">
+        <v>374</v>
+      </c>
     </row>
     <row r="380">
       <c r="A380" t="str">
@@ -20388,6 +21474,9 @@
       <c r="Q380" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R380" t="str">
+        <v>375</v>
+      </c>
     </row>
     <row r="381">
       <c r="A381" t="str">
@@ -20441,6 +21530,9 @@
       <c r="Q381" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R381" t="str">
+        <v>376</v>
+      </c>
     </row>
     <row r="382">
       <c r="A382" t="str">
@@ -20494,6 +21586,9 @@
       <c r="Q382" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R382" t="str">
+        <v>377</v>
+      </c>
     </row>
     <row r="383">
       <c r="A383" t="str">
@@ -20547,6 +21642,9 @@
       <c r="Q383" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R383" t="str">
+        <v>378</v>
+      </c>
     </row>
     <row r="384">
       <c r="A384" t="str">
@@ -20600,6 +21698,9 @@
       <c r="Q384" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R384" t="str">
+        <v>379</v>
+      </c>
     </row>
     <row r="385">
       <c r="A385" t="str">
@@ -20653,6 +21754,9 @@
       <c r="Q385" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R385" t="str">
+        <v>380</v>
+      </c>
     </row>
     <row r="386">
       <c r="A386" t="str">
@@ -20706,6 +21810,9 @@
       <c r="Q386" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R386" t="str">
+        <v>381</v>
+      </c>
     </row>
     <row r="387">
       <c r="A387" t="str">
@@ -20759,6 +21866,9 @@
       <c r="Q387" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R387" t="str">
+        <v>382</v>
+      </c>
     </row>
     <row r="388">
       <c r="A388" t="str">
@@ -20812,6 +21922,9 @@
       <c r="Q388" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R388" t="str">
+        <v>383</v>
+      </c>
     </row>
     <row r="389">
       <c r="A389" t="str">
@@ -20865,6 +21978,9 @@
       <c r="Q389" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R389" t="str">
+        <v>384</v>
+      </c>
     </row>
     <row r="390">
       <c r="A390" t="str">
@@ -20918,6 +22034,9 @@
       <c r="Q390" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R390" t="str">
+        <v>385</v>
+      </c>
     </row>
     <row r="391">
       <c r="A391" t="str">
@@ -20971,6 +22090,9 @@
       <c r="Q391" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R391" t="str">
+        <v>386</v>
+      </c>
     </row>
     <row r="392">
       <c r="A392" t="str">
@@ -21024,6 +22146,9 @@
       <c r="Q392" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R392" t="str">
+        <v>387</v>
+      </c>
     </row>
     <row r="393">
       <c r="A393" t="str">
@@ -21077,6 +22202,9 @@
       <c r="Q393" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R393" t="str">
+        <v>388</v>
+      </c>
     </row>
     <row r="394">
       <c r="A394" t="str">
@@ -21130,6 +22258,9 @@
       <c r="Q394" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R394" t="str">
+        <v>389</v>
+      </c>
     </row>
     <row r="395">
       <c r="A395" t="str">
@@ -21183,6 +22314,9 @@
       <c r="Q395" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R395" t="str">
+        <v>390</v>
+      </c>
     </row>
     <row r="396">
       <c r="A396" t="str">
@@ -21236,6 +22370,9 @@
       <c r="Q396" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R396" t="str">
+        <v>391</v>
+      </c>
     </row>
     <row r="397">
       <c r="A397" t="str">
@@ -21289,6 +22426,9 @@
       <c r="Q397" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R397" t="str">
+        <v>392</v>
+      </c>
     </row>
     <row r="398">
       <c r="A398" t="str">
@@ -21342,6 +22482,9 @@
       <c r="Q398" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R398" t="str">
+        <v>393</v>
+      </c>
     </row>
     <row r="399">
       <c r="A399" t="str">
@@ -21395,6 +22538,9 @@
       <c r="Q399" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R399" t="str">
+        <v>394</v>
+      </c>
     </row>
     <row r="400">
       <c r="A400" t="str">
@@ -21448,6 +22594,9 @@
       <c r="Q400" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R400" t="str">
+        <v>395</v>
+      </c>
     </row>
     <row r="401">
       <c r="A401" t="str">
@@ -21501,6 +22650,9 @@
       <c r="Q401" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R401" t="str">
+        <v>396</v>
+      </c>
     </row>
     <row r="402">
       <c r="A402" t="str">
@@ -21554,6 +22706,9 @@
       <c r="Q402" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R402" t="str">
+        <v>397</v>
+      </c>
     </row>
     <row r="403">
       <c r="A403" t="str">
@@ -21607,6 +22762,9 @@
       <c r="Q403" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R403" t="str">
+        <v>398</v>
+      </c>
     </row>
     <row r="404">
       <c r="A404" t="str">
@@ -21660,6 +22818,9 @@
       <c r="Q404" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R404" t="str">
+        <v>399</v>
+      </c>
     </row>
     <row r="405">
       <c r="A405" t="str">
@@ -21713,6 +22874,9 @@
       <c r="Q405" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R405" t="str">
+        <v>400</v>
+      </c>
     </row>
     <row r="406">
       <c r="A406" t="str">
@@ -21766,6 +22930,9 @@
       <c r="Q406" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R406" t="str">
+        <v>401</v>
+      </c>
     </row>
     <row r="407">
       <c r="A407" t="str">
@@ -21819,6 +22986,9 @@
       <c r="Q407" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R407" t="str">
+        <v>402</v>
+      </c>
     </row>
     <row r="408">
       <c r="A408" t="str">
@@ -21872,6 +23042,9 @@
       <c r="Q408" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R408" t="str">
+        <v>403</v>
+      </c>
     </row>
     <row r="409">
       <c r="A409" t="str">
@@ -21925,6 +23098,9 @@
       <c r="Q409" t="str">
         <v>2026-01-02</v>
       </c>
+      <c r="R409" t="str">
+        <v>404</v>
+      </c>
     </row>
     <row r="410">
       <c r="A410" t="str">
@@ -21978,6 +23154,9 @@
       <c r="Q410" t="str">
         <v>2026-01-02</v>
       </c>
+      <c r="R410" t="str">
+        <v>405</v>
+      </c>
     </row>
     <row r="411">
       <c r="A411" t="str">
@@ -22031,6 +23210,9 @@
       <c r="Q411" t="str">
         <v>2026-01-02</v>
       </c>
+      <c r="R411" t="str">
+        <v>406</v>
+      </c>
     </row>
     <row r="412">
       <c r="A412" t="str">
@@ -22084,6 +23266,9 @@
       <c r="Q412" t="str">
         <v>2026-01-02</v>
       </c>
+      <c r="R412" t="str">
+        <v>407</v>
+      </c>
     </row>
     <row r="413">
       <c r="A413" t="str">
@@ -22137,6 +23322,9 @@
       <c r="Q413" t="str">
         <v>2026-01-02</v>
       </c>
+      <c r="R413" t="str">
+        <v>408</v>
+      </c>
     </row>
     <row r="414">
       <c r="A414" t="str">
@@ -22190,6 +23378,9 @@
       <c r="Q414" t="str">
         <v>2026-01-02</v>
       </c>
+      <c r="R414" t="str">
+        <v>409</v>
+      </c>
     </row>
     <row r="415">
       <c r="A415" t="str">
@@ -22243,6 +23434,9 @@
       <c r="Q415" t="str">
         <v>2026-01-02</v>
       </c>
+      <c r="R415" t="str">
+        <v>410</v>
+      </c>
     </row>
     <row r="416">
       <c r="A416" t="str">
@@ -22296,6 +23490,9 @@
       <c r="Q416" t="str">
         <v>2026-01-02</v>
       </c>
+      <c r="R416" t="str">
+        <v>411</v>
+      </c>
     </row>
     <row r="417">
       <c r="A417" t="str">
@@ -22349,6 +23546,9 @@
       <c r="Q417" t="str">
         <v>2026-01-02</v>
       </c>
+      <c r="R417" t="str">
+        <v>412</v>
+      </c>
     </row>
     <row r="418">
       <c r="A418" t="str">
@@ -22402,6 +23602,9 @@
       <c r="Q418" t="str">
         <v>2026-01-02</v>
       </c>
+      <c r="R418" t="str">
+        <v>413</v>
+      </c>
     </row>
     <row r="419">
       <c r="A419" t="str">
@@ -22455,6 +23658,9 @@
       <c r="Q419" t="str">
         <v>2026-01-02</v>
       </c>
+      <c r="R419" t="str">
+        <v>414</v>
+      </c>
     </row>
     <row r="420">
       <c r="A420" t="str">
@@ -22508,6 +23714,9 @@
       <c r="Q420" t="str">
         <v>2026-01-02</v>
       </c>
+      <c r="R420" t="str">
+        <v>415</v>
+      </c>
     </row>
     <row r="421">
       <c r="A421" t="str">
@@ -22561,6 +23770,9 @@
       <c r="Q421" t="str">
         <v>2026-01-02</v>
       </c>
+      <c r="R421" t="str">
+        <v>416</v>
+      </c>
     </row>
     <row r="422">
       <c r="A422" t="str">
@@ -22614,6 +23826,9 @@
       <c r="Q422" t="str">
         <v>2026-01-02</v>
       </c>
+      <c r="R422" t="str">
+        <v>417</v>
+      </c>
     </row>
     <row r="423">
       <c r="A423" t="str">
@@ -22667,6 +23882,9 @@
       <c r="Q423" t="str">
         <v>2026-01-02</v>
       </c>
+      <c r="R423" t="str">
+        <v>418</v>
+      </c>
     </row>
     <row r="424">
       <c r="A424" t="str">
@@ -22720,6 +23938,9 @@
       <c r="Q424" t="str">
         <v>2026-01-02</v>
       </c>
+      <c r="R424" t="str">
+        <v>419</v>
+      </c>
     </row>
     <row r="425">
       <c r="A425" t="str">
@@ -22773,6 +23994,9 @@
       <c r="Q425" t="str">
         <v>2026-01-02</v>
       </c>
+      <c r="R425" t="str">
+        <v>420</v>
+      </c>
     </row>
     <row r="426">
       <c r="A426" t="str">
@@ -22826,6 +24050,9 @@
       <c r="Q426" t="str">
         <v>2026-01-02</v>
       </c>
+      <c r="R426" t="str">
+        <v>421</v>
+      </c>
     </row>
     <row r="427">
       <c r="A427" t="str">
@@ -22879,6 +24106,9 @@
       <c r="Q427" t="str">
         <v>2026-01-02</v>
       </c>
+      <c r="R427" t="str">
+        <v>422</v>
+      </c>
     </row>
     <row r="428">
       <c r="A428" t="str">
@@ -22932,6 +24162,9 @@
       <c r="Q428" t="str">
         <v>2026-01-02</v>
       </c>
+      <c r="R428" t="str">
+        <v>423</v>
+      </c>
     </row>
     <row r="429">
       <c r="A429" t="str">
@@ -22985,6 +24218,9 @@
       <c r="Q429" t="str">
         <v>2026-01-02</v>
       </c>
+      <c r="R429" t="str">
+        <v>424</v>
+      </c>
     </row>
     <row r="430">
       <c r="A430" t="str">
@@ -23038,6 +24274,9 @@
       <c r="Q430" t="str">
         <v>2026-01-02</v>
       </c>
+      <c r="R430" t="str">
+        <v>425</v>
+      </c>
     </row>
     <row r="431">
       <c r="A431" t="str">
@@ -23091,6 +24330,9 @@
       <c r="Q431" t="str">
         <v>2026-01-02</v>
       </c>
+      <c r="R431" t="str">
+        <v>426</v>
+      </c>
     </row>
     <row r="432">
       <c r="A432" t="str">
@@ -23144,6 +24386,9 @@
       <c r="Q432" t="str">
         <v>2026-01-02</v>
       </c>
+      <c r="R432" t="str">
+        <v>427</v>
+      </c>
     </row>
     <row r="433">
       <c r="A433" t="str">
@@ -23197,6 +24442,9 @@
       <c r="Q433" t="str">
         <v>2026-01-02</v>
       </c>
+      <c r="R433" t="str">
+        <v>428</v>
+      </c>
     </row>
     <row r="434">
       <c r="A434" t="str">
@@ -23250,6 +24498,9 @@
       <c r="Q434" t="str">
         <v>2026-01-02</v>
       </c>
+      <c r="R434" t="str">
+        <v>429</v>
+      </c>
     </row>
     <row r="435">
       <c r="A435" t="str">
@@ -23303,6 +24554,9 @@
       <c r="Q435" t="str">
         <v>2026-01-02</v>
       </c>
+      <c r="R435" t="str">
+        <v>430</v>
+      </c>
     </row>
     <row r="436">
       <c r="A436" t="str">
@@ -23356,6 +24610,9 @@
       <c r="Q436" t="str">
         <v>2026-01-02</v>
       </c>
+      <c r="R436" t="str">
+        <v>431</v>
+      </c>
     </row>
     <row r="437">
       <c r="A437" t="str">
@@ -23409,6 +24666,9 @@
       <c r="Q437" t="str">
         <v>2026-01-02</v>
       </c>
+      <c r="R437" t="str">
+        <v>432</v>
+      </c>
     </row>
     <row r="438">
       <c r="A438" t="str">
@@ -23462,6 +24722,9 @@
       <c r="Q438" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R438" t="str">
+        <v>433</v>
+      </c>
     </row>
     <row r="439">
       <c r="A439" t="str">
@@ -23515,6 +24778,9 @@
       <c r="Q439" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R439" t="str">
+        <v>434</v>
+      </c>
     </row>
     <row r="440">
       <c r="A440" t="str">
@@ -23568,6 +24834,9 @@
       <c r="Q440" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R440" t="str">
+        <v>435</v>
+      </c>
     </row>
     <row r="441">
       <c r="A441" t="str">
@@ -23621,6 +24890,9 @@
       <c r="Q441" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R441" t="str">
+        <v>436</v>
+      </c>
     </row>
     <row r="442">
       <c r="A442" t="str">
@@ -23674,6 +24946,9 @@
       <c r="Q442" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R442" t="str">
+        <v>437</v>
+      </c>
     </row>
     <row r="443">
       <c r="A443" t="str">
@@ -23727,6 +25002,9 @@
       <c r="Q443" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R443" t="str">
+        <v>438</v>
+      </c>
     </row>
     <row r="444">
       <c r="A444" t="str">
@@ -23780,6 +25058,9 @@
       <c r="Q444" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R444" t="str">
+        <v>439</v>
+      </c>
     </row>
     <row r="445">
       <c r="A445" t="str">
@@ -23833,6 +25114,9 @@
       <c r="Q445" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R445" t="str">
+        <v>440</v>
+      </c>
     </row>
     <row r="446">
       <c r="A446" t="str">
@@ -23886,6 +25170,9 @@
       <c r="Q446" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R446" t="str">
+        <v>441</v>
+      </c>
     </row>
     <row r="447">
       <c r="A447" t="str">
@@ -23939,6 +25226,9 @@
       <c r="Q447" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R447" t="str">
+        <v>442</v>
+      </c>
     </row>
     <row r="448">
       <c r="A448" t="str">
@@ -23992,6 +25282,9 @@
       <c r="Q448" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R448" t="str">
+        <v>443</v>
+      </c>
     </row>
     <row r="449">
       <c r="A449" t="str">
@@ -24045,6 +25338,9 @@
       <c r="Q449" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R449" t="str">
+        <v>444</v>
+      </c>
     </row>
     <row r="450">
       <c r="A450" t="str">
@@ -24098,6 +25394,9 @@
       <c r="Q450" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R450" t="str">
+        <v>445</v>
+      </c>
     </row>
     <row r="451">
       <c r="A451" t="str">
@@ -24151,6 +25450,9 @@
       <c r="Q451" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R451" t="str">
+        <v>446</v>
+      </c>
     </row>
     <row r="452">
       <c r="A452" t="str">
@@ -24204,6 +25506,9 @@
       <c r="Q452" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R452" t="str">
+        <v>447</v>
+      </c>
     </row>
     <row r="453">
       <c r="A453" t="str">
@@ -24257,6 +25562,9 @@
       <c r="Q453" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R453" t="str">
+        <v>448</v>
+      </c>
     </row>
     <row r="454">
       <c r="A454" t="str">
@@ -24310,6 +25618,9 @@
       <c r="Q454" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R454" t="str">
+        <v>449</v>
+      </c>
     </row>
     <row r="455">
       <c r="A455" t="str">
@@ -24363,6 +25674,9 @@
       <c r="Q455" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R455" t="str">
+        <v>450</v>
+      </c>
     </row>
     <row r="456">
       <c r="A456" t="str">
@@ -24416,6 +25730,9 @@
       <c r="Q456" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R456" t="str">
+        <v>451</v>
+      </c>
     </row>
     <row r="457">
       <c r="A457" t="str">
@@ -24469,6 +25786,9 @@
       <c r="Q457" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R457" t="str">
+        <v>452</v>
+      </c>
     </row>
     <row r="458">
       <c r="A458" t="str">
@@ -24522,6 +25842,9 @@
       <c r="Q458" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R458" t="str">
+        <v>453</v>
+      </c>
     </row>
     <row r="459">
       <c r="A459" t="str">
@@ -24575,6 +25898,9 @@
       <c r="Q459" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R459" t="str">
+        <v>454</v>
+      </c>
     </row>
     <row r="460">
       <c r="A460" t="str">
@@ -24628,6 +25954,9 @@
       <c r="Q460" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R460" t="str">
+        <v>455</v>
+      </c>
     </row>
     <row r="461">
       <c r="A461" t="str">
@@ -24681,6 +26010,9 @@
       <c r="Q461" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R461" t="str">
+        <v>456</v>
+      </c>
     </row>
     <row r="462">
       <c r="A462" t="str">
@@ -24734,6 +26066,9 @@
       <c r="Q462" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R462" t="str">
+        <v>457</v>
+      </c>
     </row>
     <row r="463">
       <c r="A463" t="str">
@@ -24787,6 +26122,9 @@
       <c r="Q463" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R463" t="str">
+        <v>458</v>
+      </c>
     </row>
     <row r="464">
       <c r="A464" t="str">
@@ -24840,6 +26178,9 @@
       <c r="Q464" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R464" t="str">
+        <v>459</v>
+      </c>
     </row>
     <row r="465">
       <c r="A465" t="str">
@@ -24893,6 +26234,9 @@
       <c r="Q465" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R465" t="str">
+        <v>460</v>
+      </c>
     </row>
     <row r="466">
       <c r="A466" t="str">
@@ -24946,6 +26290,9 @@
       <c r="Q466" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R466" t="str">
+        <v>461</v>
+      </c>
     </row>
     <row r="467">
       <c r="A467" t="str">
@@ -24999,6 +26346,9 @@
       <c r="Q467" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R467" t="str">
+        <v>462</v>
+      </c>
     </row>
     <row r="468">
       <c r="A468" t="str">
@@ -25052,6 +26402,9 @@
       <c r="Q468" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R468" t="str">
+        <v>463</v>
+      </c>
     </row>
     <row r="469">
       <c r="A469" t="str">
@@ -25105,6 +26458,9 @@
       <c r="Q469" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R469" t="str">
+        <v>464</v>
+      </c>
     </row>
     <row r="470">
       <c r="A470" t="str">
@@ -25158,6 +26514,9 @@
       <c r="Q470" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R470" t="str">
+        <v>465</v>
+      </c>
     </row>
     <row r="471">
       <c r="A471" t="str">
@@ -25211,6 +26570,9 @@
       <c r="Q471" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R471" t="str">
+        <v>466</v>
+      </c>
     </row>
     <row r="472">
       <c r="A472" t="str">
@@ -25264,6 +26626,9 @@
       <c r="Q472" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R472" t="str">
+        <v>467</v>
+      </c>
     </row>
     <row r="473">
       <c r="A473" t="str">
@@ -25317,6 +26682,9 @@
       <c r="Q473" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R473" t="str">
+        <v>468</v>
+      </c>
     </row>
     <row r="474">
       <c r="A474" t="str">
@@ -25370,6 +26738,9 @@
       <c r="Q474" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R474" t="str">
+        <v>469</v>
+      </c>
     </row>
     <row r="475">
       <c r="A475" t="str">
@@ -25423,6 +26794,9 @@
       <c r="Q475" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R475" t="str">
+        <v>470</v>
+      </c>
     </row>
     <row r="476">
       <c r="A476" t="str">
@@ -25476,6 +26850,9 @@
       <c r="Q476" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R476" t="str">
+        <v>471</v>
+      </c>
     </row>
     <row r="477">
       <c r="A477" t="str">
@@ -25529,6 +26906,9 @@
       <c r="Q477" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R477" t="str">
+        <v>472</v>
+      </c>
     </row>
     <row r="478">
       <c r="A478" t="str">
@@ -25582,6 +26962,9 @@
       <c r="Q478" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R478" t="str">
+        <v>473</v>
+      </c>
     </row>
     <row r="479">
       <c r="A479" t="str">
@@ -25635,6 +27018,9 @@
       <c r="Q479" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R479" t="str">
+        <v>474</v>
+      </c>
     </row>
     <row r="480">
       <c r="A480" t="str">
@@ -25688,6 +27074,9 @@
       <c r="Q480" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R480" t="str">
+        <v>475</v>
+      </c>
     </row>
     <row r="481">
       <c r="A481" t="str">
@@ -25741,6 +27130,9 @@
       <c r="Q481" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R481" t="str">
+        <v>476</v>
+      </c>
     </row>
     <row r="482">
       <c r="A482" t="str">
@@ -25794,6 +27186,9 @@
       <c r="Q482" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R482" t="str">
+        <v>477</v>
+      </c>
     </row>
     <row r="483">
       <c r="A483" t="str">
@@ -25847,6 +27242,9 @@
       <c r="Q483" t="str">
         <v>2026-01-02</v>
       </c>
+      <c r="R483" t="str">
+        <v>478</v>
+      </c>
     </row>
     <row r="484">
       <c r="A484" t="str">
@@ -25900,6 +27298,9 @@
       <c r="Q484" t="str">
         <v>2026-01-02</v>
       </c>
+      <c r="R484" t="str">
+        <v>479</v>
+      </c>
     </row>
     <row r="485">
       <c r="A485" t="str">
@@ -25953,6 +27354,9 @@
       <c r="Q485" t="str">
         <v>2026-01-02</v>
       </c>
+      <c r="R485" t="str">
+        <v>480</v>
+      </c>
     </row>
     <row r="486">
       <c r="A486" t="str">
@@ -26006,6 +27410,9 @@
       <c r="Q486" t="str">
         <v>2026-01-02</v>
       </c>
+      <c r="R486" t="str">
+        <v>481</v>
+      </c>
     </row>
     <row r="487">
       <c r="A487" t="str">
@@ -26059,6 +27466,9 @@
       <c r="Q487" t="str">
         <v>2026-01-02</v>
       </c>
+      <c r="R487" t="str">
+        <v>482</v>
+      </c>
     </row>
     <row r="488">
       <c r="A488" t="str">
@@ -26112,6 +27522,9 @@
       <c r="Q488" t="str">
         <v>2026-01-02</v>
       </c>
+      <c r="R488" t="str">
+        <v>483</v>
+      </c>
     </row>
     <row r="489">
       <c r="A489" t="str">
@@ -26165,6 +27578,9 @@
       <c r="Q489" t="str">
         <v>2026-01-02</v>
       </c>
+      <c r="R489" t="str">
+        <v>484</v>
+      </c>
     </row>
     <row r="490">
       <c r="A490" t="str">
@@ -26218,6 +27634,9 @@
       <c r="Q490" t="str">
         <v>2026-01-02</v>
       </c>
+      <c r="R490" t="str">
+        <v>485</v>
+      </c>
     </row>
     <row r="491">
       <c r="A491" t="str">
@@ -26271,6 +27690,9 @@
       <c r="Q491" t="str">
         <v>2026-01-02</v>
       </c>
+      <c r="R491" t="str">
+        <v>486</v>
+      </c>
     </row>
     <row r="492">
       <c r="A492" t="str">
@@ -26324,6 +27746,9 @@
       <c r="Q492" t="str">
         <v>2026-01-02</v>
       </c>
+      <c r="R492" t="str">
+        <v>487</v>
+      </c>
     </row>
     <row r="493">
       <c r="A493" t="str">
@@ -26377,6 +27802,9 @@
       <c r="Q493" t="str">
         <v>2026-01-02</v>
       </c>
+      <c r="R493" t="str">
+        <v>488</v>
+      </c>
     </row>
     <row r="494">
       <c r="A494" t="str">
@@ -26430,6 +27858,9 @@
       <c r="Q494" t="str">
         <v>2026-01-02</v>
       </c>
+      <c r="R494" t="str">
+        <v>489</v>
+      </c>
     </row>
     <row r="495">
       <c r="A495" t="str">
@@ -26483,6 +27914,9 @@
       <c r="Q495" t="str">
         <v>2026-01-02</v>
       </c>
+      <c r="R495" t="str">
+        <v>490</v>
+      </c>
     </row>
     <row r="496">
       <c r="A496" t="str">
@@ -26536,6 +27970,9 @@
       <c r="Q496" t="str">
         <v>2026-01-02</v>
       </c>
+      <c r="R496" t="str">
+        <v>491</v>
+      </c>
     </row>
     <row r="497">
       <c r="A497" t="str">
@@ -26589,6 +28026,9 @@
       <c r="Q497" t="str">
         <v>2026-01-02</v>
       </c>
+      <c r="R497" t="str">
+        <v>492</v>
+      </c>
     </row>
     <row r="498">
       <c r="A498" t="str">
@@ -26642,6 +28082,9 @@
       <c r="Q498" t="str">
         <v>2026-01-02</v>
       </c>
+      <c r="R498" t="str">
+        <v>493</v>
+      </c>
     </row>
     <row r="499">
       <c r="A499" t="str">
@@ -26695,6 +28138,9 @@
       <c r="Q499" t="str">
         <v>2026-01-02</v>
       </c>
+      <c r="R499" t="str">
+        <v>494</v>
+      </c>
     </row>
     <row r="500">
       <c r="A500" t="str">
@@ -26748,6 +28194,9 @@
       <c r="Q500" t="str">
         <v>2026-01-02</v>
       </c>
+      <c r="R500" t="str">
+        <v>495</v>
+      </c>
     </row>
     <row r="501">
       <c r="A501" t="str">
@@ -26801,6 +28250,9 @@
       <c r="Q501" t="str">
         <v>2026-01-02</v>
       </c>
+      <c r="R501" t="str">
+        <v>496</v>
+      </c>
     </row>
     <row r="502">
       <c r="A502" t="str">
@@ -26854,6 +28306,9 @@
       <c r="Q502" t="str">
         <v>2026-01-02</v>
       </c>
+      <c r="R502" t="str">
+        <v>497</v>
+      </c>
     </row>
     <row r="503">
       <c r="A503" t="str">
@@ -26907,6 +28362,9 @@
       <c r="Q503" t="str">
         <v>2026-01-02</v>
       </c>
+      <c r="R503" t="str">
+        <v>498</v>
+      </c>
     </row>
     <row r="504">
       <c r="A504" t="str">
@@ -26960,6 +28418,9 @@
       <c r="Q504" t="str">
         <v>2026-01-02</v>
       </c>
+      <c r="R504" t="str">
+        <v>499</v>
+      </c>
     </row>
     <row r="505">
       <c r="A505" t="str">
@@ -27013,6 +28474,9 @@
       <c r="Q505" t="str">
         <v>2026-01-02</v>
       </c>
+      <c r="R505" t="str">
+        <v>500</v>
+      </c>
     </row>
     <row r="506">
       <c r="A506" t="str">
@@ -27066,6 +28530,9 @@
       <c r="Q506" t="str">
         <v>2026-01-02</v>
       </c>
+      <c r="R506" t="str">
+        <v>501</v>
+      </c>
     </row>
     <row r="507">
       <c r="A507" t="str">
@@ -27119,6 +28586,9 @@
       <c r="Q507" t="str">
         <v>2026-01-02</v>
       </c>
+      <c r="R507" t="str">
+        <v>502</v>
+      </c>
     </row>
     <row r="508">
       <c r="A508" t="str">
@@ -27172,6 +28642,9 @@
       <c r="Q508" t="str">
         <v>2026-01-02</v>
       </c>
+      <c r="R508" t="str">
+        <v>503</v>
+      </c>
     </row>
     <row r="509">
       <c r="A509" t="str">
@@ -27225,6 +28698,9 @@
       <c r="Q509" t="str">
         <v>2026-01-02</v>
       </c>
+      <c r="R509" t="str">
+        <v>504</v>
+      </c>
     </row>
     <row r="510">
       <c r="A510" t="str">
@@ -27278,6 +28754,9 @@
       <c r="Q510" t="str">
         <v>2026-01-02</v>
       </c>
+      <c r="R510" t="str">
+        <v>505</v>
+      </c>
     </row>
     <row r="511">
       <c r="A511" t="str">
@@ -27331,6 +28810,9 @@
       <c r="Q511" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R511" t="str">
+        <v>506</v>
+      </c>
     </row>
     <row r="512">
       <c r="A512" t="str">
@@ -27384,6 +28866,9 @@
       <c r="Q512" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R512" t="str">
+        <v>507</v>
+      </c>
     </row>
     <row r="513">
       <c r="A513" t="str">
@@ -27437,6 +28922,9 @@
       <c r="Q513" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R513" t="str">
+        <v>508</v>
+      </c>
     </row>
     <row r="514">
       <c r="A514" t="str">
@@ -27490,6 +28978,9 @@
       <c r="Q514" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R514" t="str">
+        <v>509</v>
+      </c>
     </row>
     <row r="515">
       <c r="A515" t="str">
@@ -27543,6 +29034,9 @@
       <c r="Q515" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R515" t="str">
+        <v>510</v>
+      </c>
     </row>
     <row r="516">
       <c r="A516" t="str">
@@ -27596,6 +29090,9 @@
       <c r="Q516" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R516" t="str">
+        <v>511</v>
+      </c>
     </row>
     <row r="517">
       <c r="A517" t="str">
@@ -27649,6 +29146,9 @@
       <c r="Q517" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R517" t="str">
+        <v>512</v>
+      </c>
     </row>
     <row r="518">
       <c r="A518" t="str">
@@ -27702,6 +29202,9 @@
       <c r="Q518" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R518" t="str">
+        <v>513</v>
+      </c>
     </row>
     <row r="519">
       <c r="A519" t="str">
@@ -27755,6 +29258,9 @@
       <c r="Q519" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R519" t="str">
+        <v>514</v>
+      </c>
     </row>
     <row r="520">
       <c r="A520" t="str">
@@ -27808,6 +29314,9 @@
       <c r="Q520" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R520" t="str">
+        <v>515</v>
+      </c>
     </row>
     <row r="521">
       <c r="A521" t="str">
@@ -27861,6 +29370,9 @@
       <c r="Q521" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R521" t="str">
+        <v>516</v>
+      </c>
     </row>
     <row r="522">
       <c r="A522" t="str">
@@ -27914,6 +29426,9 @@
       <c r="Q522" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R522" t="str">
+        <v>517</v>
+      </c>
     </row>
     <row r="523">
       <c r="A523" t="str">
@@ -27967,6 +29482,9 @@
       <c r="Q523" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R523" t="str">
+        <v>518</v>
+      </c>
     </row>
     <row r="524">
       <c r="A524" t="str">
@@ -28020,6 +29538,9 @@
       <c r="Q524" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R524" t="str">
+        <v>519</v>
+      </c>
     </row>
     <row r="525">
       <c r="A525" t="str">
@@ -28073,6 +29594,9 @@
       <c r="Q525" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R525" t="str">
+        <v>520</v>
+      </c>
     </row>
     <row r="526">
       <c r="A526" t="str">
@@ -28126,6 +29650,9 @@
       <c r="Q526" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R526" t="str">
+        <v>521</v>
+      </c>
     </row>
     <row r="527">
       <c r="A527" t="str">
@@ -28179,6 +29706,9 @@
       <c r="Q527" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R527" t="str">
+        <v>522</v>
+      </c>
     </row>
     <row r="528">
       <c r="A528" t="str">
@@ -28232,6 +29762,9 @@
       <c r="Q528" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R528" t="str">
+        <v>523</v>
+      </c>
     </row>
     <row r="529">
       <c r="A529" t="str">
@@ -28285,6 +29818,9 @@
       <c r="Q529" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R529" t="str">
+        <v>524</v>
+      </c>
     </row>
     <row r="530">
       <c r="A530" t="str">
@@ -28338,6 +29874,9 @@
       <c r="Q530" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R530" t="str">
+        <v>525</v>
+      </c>
     </row>
     <row r="531">
       <c r="A531" t="str">
@@ -28391,6 +29930,9 @@
       <c r="Q531" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R531" t="str">
+        <v>526</v>
+      </c>
     </row>
     <row r="532">
       <c r="A532" t="str">
@@ -28444,6 +29986,9 @@
       <c r="Q532" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R532" t="str">
+        <v>527</v>
+      </c>
     </row>
     <row r="533">
       <c r="A533" t="str">
@@ -28497,6 +30042,9 @@
       <c r="Q533" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R533" t="str">
+        <v>528</v>
+      </c>
     </row>
     <row r="534">
       <c r="A534" t="str">
@@ -28550,6 +30098,9 @@
       <c r="Q534" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R534" t="str">
+        <v>529</v>
+      </c>
     </row>
     <row r="535">
       <c r="A535" t="str">
@@ -28603,6 +30154,9 @@
       <c r="Q535" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R535" t="str">
+        <v>530</v>
+      </c>
     </row>
     <row r="536">
       <c r="A536" t="str">
@@ -28656,6 +30210,9 @@
       <c r="Q536" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R536" t="str">
+        <v>531</v>
+      </c>
     </row>
     <row r="537">
       <c r="A537" t="str">
@@ -28709,6 +30266,9 @@
       <c r="Q537" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R537" t="str">
+        <v>532</v>
+      </c>
     </row>
     <row r="538">
       <c r="A538" t="str">
@@ -28762,6 +30322,9 @@
       <c r="Q538" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R538" t="str">
+        <v>533</v>
+      </c>
     </row>
     <row r="539">
       <c r="A539" t="str">
@@ -28815,6 +30378,9 @@
       <c r="Q539" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R539" t="str">
+        <v>534</v>
+      </c>
     </row>
     <row r="540">
       <c r="A540" t="str">
@@ -28868,6 +30434,9 @@
       <c r="Q540" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R540" t="str">
+        <v>535</v>
+      </c>
     </row>
     <row r="541">
       <c r="A541" t="str">
@@ -28921,6 +30490,9 @@
       <c r="Q541" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R541" t="str">
+        <v>536</v>
+      </c>
     </row>
     <row r="542">
       <c r="A542" t="str">
@@ -28974,6 +30546,9 @@
       <c r="Q542" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R542" t="str">
+        <v>537</v>
+      </c>
     </row>
     <row r="543">
       <c r="A543" t="str">
@@ -29027,6 +30602,9 @@
       <c r="Q543" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R543" t="str">
+        <v>538</v>
+      </c>
     </row>
     <row r="544">
       <c r="A544" t="str">
@@ -29080,6 +30658,9 @@
       <c r="Q544" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R544" t="str">
+        <v>539</v>
+      </c>
     </row>
     <row r="545">
       <c r="A545" t="str">
@@ -29133,6 +30714,9 @@
       <c r="Q545" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R545" t="str">
+        <v>540</v>
+      </c>
     </row>
     <row r="546">
       <c r="A546" t="str">
@@ -29186,6 +30770,9 @@
       <c r="Q546" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R546" t="str">
+        <v>541</v>
+      </c>
     </row>
     <row r="547">
       <c r="A547" t="str">
@@ -29239,6 +30826,9 @@
       <c r="Q547" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R547" t="str">
+        <v>542</v>
+      </c>
     </row>
     <row r="548">
       <c r="A548" t="str">
@@ -29292,6 +30882,9 @@
       <c r="Q548" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R548" t="str">
+        <v>543</v>
+      </c>
     </row>
     <row r="549">
       <c r="A549" t="str">
@@ -29345,6 +30938,9 @@
       <c r="Q549" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R549" t="str">
+        <v>544</v>
+      </c>
     </row>
     <row r="550">
       <c r="A550" t="str">
@@ -29398,6 +30994,9 @@
       <c r="Q550" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R550" t="str">
+        <v>545</v>
+      </c>
     </row>
     <row r="551">
       <c r="A551" t="str">
@@ -29451,6 +31050,9 @@
       <c r="Q551" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R551" t="str">
+        <v>546</v>
+      </c>
     </row>
     <row r="552">
       <c r="A552" t="str">
@@ -29504,6 +31106,9 @@
       <c r="Q552" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R552" t="str">
+        <v>547</v>
+      </c>
     </row>
     <row r="553">
       <c r="A553" t="str">
@@ -29557,6 +31162,9 @@
       <c r="Q553" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R553" t="str">
+        <v>548</v>
+      </c>
     </row>
     <row r="554">
       <c r="A554" t="str">
@@ -29610,6 +31218,9 @@
       <c r="Q554" t="str">
         <v>2026-01-02</v>
       </c>
+      <c r="R554" t="str">
+        <v>549</v>
+      </c>
     </row>
     <row r="555">
       <c r="A555" t="str">
@@ -29663,6 +31274,9 @@
       <c r="Q555" t="str">
         <v>2026-01-02</v>
       </c>
+      <c r="R555" t="str">
+        <v>550</v>
+      </c>
     </row>
     <row r="556">
       <c r="A556" t="str">
@@ -29716,6 +31330,9 @@
       <c r="Q556" t="str">
         <v>2026-01-02</v>
       </c>
+      <c r="R556" t="str">
+        <v>551</v>
+      </c>
     </row>
     <row r="557">
       <c r="A557" t="str">
@@ -29769,6 +31386,9 @@
       <c r="Q557" t="str">
         <v>2026-01-02</v>
       </c>
+      <c r="R557" t="str">
+        <v>552</v>
+      </c>
     </row>
     <row r="558">
       <c r="A558" t="str">
@@ -29822,6 +31442,9 @@
       <c r="Q558" t="str">
         <v>2026-01-02</v>
       </c>
+      <c r="R558" t="str">
+        <v>553</v>
+      </c>
     </row>
     <row r="559">
       <c r="A559" t="str">
@@ -29875,6 +31498,9 @@
       <c r="Q559" t="str">
         <v>2026-01-02</v>
       </c>
+      <c r="R559" t="str">
+        <v>609</v>
+      </c>
     </row>
     <row r="560">
       <c r="A560" t="str">
@@ -29928,6 +31554,9 @@
       <c r="Q560" t="str">
         <v>2026-01-02</v>
       </c>
+      <c r="R560" t="str">
+        <v>554</v>
+      </c>
     </row>
     <row r="561">
       <c r="A561" t="str">
@@ -29981,6 +31610,9 @@
       <c r="Q561" t="str">
         <v>2026-01-02</v>
       </c>
+      <c r="R561" t="str">
+        <v>555</v>
+      </c>
     </row>
     <row r="562">
       <c r="A562" t="str">
@@ -30034,6 +31666,9 @@
       <c r="Q562" t="str">
         <v>2026-01-02</v>
       </c>
+      <c r="R562" t="str">
+        <v>556</v>
+      </c>
     </row>
     <row r="563">
       <c r="A563" t="str">
@@ -30087,6 +31722,9 @@
       <c r="Q563" t="str">
         <v>2026-01-02</v>
       </c>
+      <c r="R563" t="str">
+        <v>557</v>
+      </c>
     </row>
     <row r="564">
       <c r="A564" t="str">
@@ -30140,6 +31778,9 @@
       <c r="Q564" t="str">
         <v>2026-01-02</v>
       </c>
+      <c r="R564" t="str">
+        <v>558</v>
+      </c>
     </row>
     <row r="565">
       <c r="A565" t="str">
@@ -30193,6 +31834,9 @@
       <c r="Q565" t="str">
         <v>2026-01-02</v>
       </c>
+      <c r="R565" t="str">
+        <v>559</v>
+      </c>
     </row>
     <row r="566">
       <c r="A566" t="str">
@@ -30246,6 +31890,9 @@
       <c r="Q566" t="str">
         <v>2026-01-02</v>
       </c>
+      <c r="R566" t="str">
+        <v>560</v>
+      </c>
     </row>
     <row r="567">
       <c r="A567" t="str">
@@ -30299,6 +31946,9 @@
       <c r="Q567" t="str">
         <v>2026-01-02</v>
       </c>
+      <c r="R567" t="str">
+        <v>561</v>
+      </c>
     </row>
     <row r="568">
       <c r="A568" t="str">
@@ -30352,6 +32002,9 @@
       <c r="Q568" t="str">
         <v>2026-01-02</v>
       </c>
+      <c r="R568" t="str">
+        <v>562</v>
+      </c>
     </row>
     <row r="569">
       <c r="A569" t="str">
@@ -30405,6 +32058,9 @@
       <c r="Q569" t="str">
         <v>2026-01-02</v>
       </c>
+      <c r="R569" t="str">
+        <v>563</v>
+      </c>
     </row>
     <row r="570">
       <c r="A570" t="str">
@@ -30458,6 +32114,9 @@
       <c r="Q570" t="str">
         <v>2026-01-02</v>
       </c>
+      <c r="R570" t="str">
+        <v>564</v>
+      </c>
     </row>
     <row r="571">
       <c r="A571" t="str">
@@ -30511,6 +32170,9 @@
       <c r="Q571" t="str">
         <v>2026-01-02</v>
       </c>
+      <c r="R571" t="str">
+        <v>565</v>
+      </c>
     </row>
     <row r="572">
       <c r="A572" t="str">
@@ -30564,6 +32226,9 @@
       <c r="Q572" t="str">
         <v>2026-01-02</v>
       </c>
+      <c r="R572" t="str">
+        <v>566</v>
+      </c>
     </row>
     <row r="573">
       <c r="A573" t="str">
@@ -30617,6 +32282,9 @@
       <c r="Q573" t="str">
         <v>2026-01-02</v>
       </c>
+      <c r="R573" t="str">
+        <v>610</v>
+      </c>
     </row>
     <row r="574">
       <c r="A574" t="str">
@@ -30670,6 +32338,9 @@
       <c r="Q574" t="str">
         <v>2026-01-02</v>
       </c>
+      <c r="R574" t="str">
+        <v>567</v>
+      </c>
     </row>
     <row r="575">
       <c r="A575" t="str">
@@ -30723,6 +32394,9 @@
       <c r="Q575" t="str">
         <v>2026-01-02</v>
       </c>
+      <c r="R575" t="str">
+        <v>568</v>
+      </c>
     </row>
     <row r="576">
       <c r="A576" t="str">
@@ -30776,6 +32450,9 @@
       <c r="Q576" t="str">
         <v>2026-01-02</v>
       </c>
+      <c r="R576" t="str">
+        <v>569</v>
+      </c>
     </row>
     <row r="577">
       <c r="A577" t="str">
@@ -30829,6 +32506,9 @@
       <c r="Q577" t="str">
         <v>2026-01-02</v>
       </c>
+      <c r="R577" t="str">
+        <v>570</v>
+      </c>
     </row>
     <row r="578">
       <c r="A578" t="str">
@@ -30882,6 +32562,9 @@
       <c r="Q578" t="str">
         <v>2026-01-02</v>
       </c>
+      <c r="R578" t="str">
+        <v>571</v>
+      </c>
     </row>
     <row r="579">
       <c r="A579" t="str">
@@ -30935,6 +32618,9 @@
       <c r="Q579" t="str">
         <v>2026-01-02</v>
       </c>
+      <c r="R579" t="str">
+        <v>572</v>
+      </c>
     </row>
     <row r="580">
       <c r="A580" t="str">
@@ -30988,6 +32674,9 @@
       <c r="Q580" t="str">
         <v>2026-01-02</v>
       </c>
+      <c r="R580" t="str">
+        <v>573</v>
+      </c>
     </row>
     <row r="581">
       <c r="A581" t="str">
@@ -31041,6 +32730,9 @@
       <c r="Q581" t="str">
         <v>2026-01-02</v>
       </c>
+      <c r="R581" t="str">
+        <v>574</v>
+      </c>
     </row>
     <row r="582">
       <c r="A582" t="str">
@@ -31094,6 +32786,9 @@
       <c r="Q582" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R582" t="str">
+        <v>575</v>
+      </c>
     </row>
     <row r="583">
       <c r="A583" t="str">
@@ -31147,6 +32842,9 @@
       <c r="Q583" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R583" t="str">
+        <v>576</v>
+      </c>
     </row>
     <row r="584">
       <c r="A584" t="str">
@@ -31200,6 +32898,9 @@
       <c r="Q584" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R584" t="str">
+        <v>577</v>
+      </c>
     </row>
     <row r="585">
       <c r="A585" t="str">
@@ -31253,6 +32954,9 @@
       <c r="Q585" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R585" t="str">
+        <v>578</v>
+      </c>
     </row>
     <row r="586">
       <c r="A586" t="str">
@@ -31306,6 +33010,9 @@
       <c r="Q586" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R586" t="str">
+        <v>579</v>
+      </c>
     </row>
     <row r="587">
       <c r="A587" t="str">
@@ -31359,6 +33066,9 @@
       <c r="Q587" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R587" t="str">
+        <v>580</v>
+      </c>
     </row>
     <row r="588">
       <c r="A588" t="str">
@@ -31412,6 +33122,9 @@
       <c r="Q588" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R588" t="str">
+        <v>581</v>
+      </c>
     </row>
     <row r="589">
       <c r="A589" t="str">
@@ -31465,6 +33178,9 @@
       <c r="Q589" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R589" t="str">
+        <v>582</v>
+      </c>
     </row>
     <row r="590">
       <c r="A590" t="str">
@@ -31518,6 +33234,9 @@
       <c r="Q590" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R590" t="str">
+        <v>583</v>
+      </c>
     </row>
     <row r="591">
       <c r="A591" t="str">
@@ -31571,6 +33290,9 @@
       <c r="Q591" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R591" t="str">
+        <v>584</v>
+      </c>
     </row>
     <row r="592">
       <c r="A592" t="str">
@@ -31624,6 +33346,9 @@
       <c r="Q592" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R592" t="str">
+        <v>585</v>
+      </c>
     </row>
     <row r="593">
       <c r="A593" t="str">
@@ -31677,6 +33402,9 @@
       <c r="Q593" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R593" t="str">
+        <v>586</v>
+      </c>
     </row>
     <row r="594">
       <c r="A594" t="str">
@@ -31730,6 +33458,9 @@
       <c r="Q594" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R594" t="str">
+        <v>587</v>
+      </c>
     </row>
     <row r="595">
       <c r="A595" t="str">
@@ -31783,6 +33514,9 @@
       <c r="Q595" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R595" t="str">
+        <v>588</v>
+      </c>
     </row>
     <row r="596">
       <c r="A596" t="str">
@@ -31836,6 +33570,9 @@
       <c r="Q596" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R596" t="str">
+        <v>589</v>
+      </c>
     </row>
     <row r="597">
       <c r="A597" t="str">
@@ -31889,6 +33626,9 @@
       <c r="Q597" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R597" t="str">
+        <v>590</v>
+      </c>
     </row>
     <row r="598">
       <c r="A598" t="str">
@@ -31942,6 +33682,9 @@
       <c r="Q598" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R598" t="str">
+        <v>591</v>
+      </c>
     </row>
     <row r="599">
       <c r="A599" t="str">
@@ -31995,6 +33738,9 @@
       <c r="Q599" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R599" t="str">
+        <v>592</v>
+      </c>
     </row>
     <row r="600">
       <c r="A600" t="str">
@@ -32048,6 +33794,9 @@
       <c r="Q600" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R600" t="str">
+        <v>593</v>
+      </c>
     </row>
     <row r="601">
       <c r="A601" t="str">
@@ -32101,6 +33850,9 @@
       <c r="Q601" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R601" t="str">
+        <v>594</v>
+      </c>
     </row>
     <row r="602">
       <c r="A602" t="str">
@@ -32154,6 +33906,9 @@
       <c r="Q602" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R602" t="str">
+        <v>595</v>
+      </c>
     </row>
     <row r="603">
       <c r="A603" t="str">
@@ -32207,6 +33962,9 @@
       <c r="Q603" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R603" t="str">
+        <v>596</v>
+      </c>
     </row>
     <row r="604">
       <c r="A604" t="str">
@@ -32260,6 +34018,9 @@
       <c r="Q604" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R604" t="str">
+        <v>597</v>
+      </c>
     </row>
     <row r="605">
       <c r="A605" t="str">
@@ -32313,6 +34074,9 @@
       <c r="Q605" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R605" t="str">
+        <v>598</v>
+      </c>
     </row>
     <row r="606">
       <c r="A606" t="str">
@@ -32366,6 +34130,9 @@
       <c r="Q606" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R606" t="str">
+        <v>599</v>
+      </c>
     </row>
     <row r="607">
       <c r="A607" t="str">
@@ -32419,6 +34186,9 @@
       <c r="Q607" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R607" t="str">
+        <v>600</v>
+      </c>
     </row>
     <row r="608">
       <c r="A608" t="str">
@@ -32472,6 +34242,9 @@
       <c r="Q608" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R608" t="str">
+        <v>601</v>
+      </c>
     </row>
     <row r="609">
       <c r="A609" t="str">
@@ -32525,6 +34298,9 @@
       <c r="Q609" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R609" t="str">
+        <v>602</v>
+      </c>
     </row>
     <row r="610">
       <c r="A610" t="str">
@@ -32578,6 +34354,9 @@
       <c r="Q610" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R610" t="str">
+        <v>603</v>
+      </c>
     </row>
     <row r="611">
       <c r="A611" t="str">
@@ -32631,6 +34410,9 @@
       <c r="Q611" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R611" t="str">
+        <v>604</v>
+      </c>
     </row>
     <row r="612">
       <c r="A612" t="str">
@@ -32684,6 +34466,9 @@
       <c r="Q612" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R612" t="str">
+        <v>605</v>
+      </c>
     </row>
     <row r="613">
       <c r="A613" t="str">
@@ -32737,6 +34522,9 @@
       <c r="Q613" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R613" t="str">
+        <v>606</v>
+      </c>
     </row>
     <row r="614">
       <c r="A614" t="str">
@@ -32790,6 +34578,9 @@
       <c r="Q614" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R614" t="str">
+        <v>607</v>
+      </c>
     </row>
     <row r="615">
       <c r="A615" t="str">
@@ -32843,6 +34634,9 @@
       <c r="Q615" t="str">
         <v>2026-01-01</v>
       </c>
+      <c r="R615" t="str">
+        <v>611</v>
+      </c>
     </row>
     <row r="616">
       <c r="A616" t="str">
@@ -32895,6 +34689,9 @@
       </c>
       <c r="Q616" t="str">
         <v>2026-01-01</v>
+      </c>
+      <c r="R616" t="str">
+        <v>608</v>
       </c>
     </row>
   </sheetData>
